--- a/data/finAlign/File1/RPT_RPT7156946910381YQ_finAlign.xlsx
+++ b/data/finAlign/File1/RPT_RPT7156946910381YQ_finAlign.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FinAlign" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FinAlign" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2132,7 +2132,7 @@
         <v>8.49317901589669</v>
       </c>
       <c r="W5" t="n">
-        <v>32543.16480120758</v>
+        <v>32543.16480120757</v>
       </c>
       <c r="X5" t="n">
         <v>27249.71582945404</v>
@@ -2312,13 +2312,13 @@
         <v>40911.96104244291</v>
       </c>
       <c r="CN5" t="n">
-        <v>22734.32399154629</v>
+        <v>22734.32399154628</v>
       </c>
       <c r="CO5" t="n">
         <v>40911.96104244291</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="CR5" t="n">
         <v>20660.54032643367</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="DA5" t="n">
-        <v>22734.32399154629</v>
+        <v>22734.32399154628</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -2399,13 +2399,13 @@
         <v>48722.2946062967</v>
       </c>
       <c r="DU5" t="n">
-        <v>27813.21107780543</v>
+        <v>27813.21107780542</v>
       </c>
       <c r="DV5" t="n">
         <v>48722.2946062967</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.5708518308210169</v>
+        <v>0.5708518308210168</v>
       </c>
       <c r="DY5" t="n">
         <v>24604.75877617983</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="EH5" t="n">
-        <v>27813.21107780543</v>
+        <v>27813.21107780542</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.5708518308210169</v>
+        <v>0.5708518308210168</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>11354.04826227252</v>
       </c>
       <c r="Z6" t="n">
-        <v>5928.628549142526</v>
+        <v>5928.628549142525</v>
       </c>
       <c r="AA6" t="n">
         <v>11354.04826227252</v>
@@ -2634,7 +2634,7 @@
         <v>0.522159886253285</v>
       </c>
       <c r="AD6" t="n">
-        <v>5733.794372447622</v>
+        <v>5733.794372447621</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>5928.628549142526</v>
+        <v>5928.628549142525</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -2799,13 +2799,13 @@
         <v>17046.65043435121</v>
       </c>
       <c r="CN6" t="n">
-        <v>9472.63499647762</v>
+        <v>9472.634996477618</v>
       </c>
       <c r="CO6" t="n">
         <v>17046.65043435121</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5556889333161329</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="CR6" t="n">
         <v>8608.558469347363</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>9472.63499647762</v>
+        <v>9472.634996477618</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.5556889333161329</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>20300.95608595696</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.5708518308210168</v>
+        <v>0.5708518308210166</v>
       </c>
       <c r="DY6" t="n">
         <v>10251.98282340826</v>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.5708518308210168</v>
+        <v>0.5708518308210166</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>13624.85791472702</v>
       </c>
       <c r="Z7" t="n">
-        <v>7114.354258971031</v>
+        <v>7114.35425897103</v>
       </c>
       <c r="AA7" t="n">
         <v>13624.85791472702</v>
@@ -3121,7 +3121,7 @@
         <v>0.522159886253285</v>
       </c>
       <c r="AD7" t="n">
-        <v>6880.553246937145</v>
+        <v>6880.553246937144</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>7114.354258971031</v>
+        <v>7114.35425897103</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -3286,13 +3286,13 @@
         <v>20455.98052122146</v>
       </c>
       <c r="CN7" t="n">
-        <v>11367.16199577315</v>
+        <v>11367.16199577314</v>
       </c>
       <c r="CO7" t="n">
         <v>20455.98052122146</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="CR7" t="n">
         <v>10330.27016321684</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="DA7" t="n">
-        <v>11367.16199577315</v>
+        <v>11367.16199577314</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3373,13 +3373,13 @@
         <v>24361.14730314835</v>
       </c>
       <c r="DU7" t="n">
-        <v>13906.60553890272</v>
+        <v>13906.60553890271</v>
       </c>
       <c r="DV7" t="n">
         <v>24361.14730314835</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.5708518308210169</v>
+        <v>0.5708518308210168</v>
       </c>
       <c r="DY7" t="n">
         <v>12302.37938808992</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>13906.60553890272</v>
+        <v>13906.60553890271</v>
       </c>
       <c r="EI7" t="n">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.5708518308210169</v>
+        <v>0.5708518308210168</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0.004877817025858161</v>
       </c>
       <c r="R8" t="n">
-        <v>25752.41281189504</v>
+        <v>25752.41281189503</v>
       </c>
       <c r="S8" t="n">
         <v>21563.54292317911</v>
@@ -3593,16 +3593,16 @@
         <v>6.541741590729971</v>
       </c>
       <c r="W8" t="n">
-        <v>25065.87630798489</v>
+        <v>25065.87630798488</v>
       </c>
       <c r="X8" t="n">
-        <v>20988.67797834731</v>
+        <v>20988.6779783473</v>
       </c>
       <c r="Z8" t="n">
         <v>10959.44570578066</v>
       </c>
       <c r="AA8" t="n">
-        <v>20988.67797834731</v>
+        <v>20988.6779783473</v>
       </c>
       <c r="AB8" t="n">
         <v>0.5221598862532851</v>
@@ -3770,13 +3770,13 @@
         <v>37247.15824620525</v>
       </c>
       <c r="CL8" t="n">
-        <v>31188.56091175667</v>
+        <v>31188.56091175668</v>
       </c>
       <c r="CN8" t="n">
         <v>17331.13814471931</v>
       </c>
       <c r="CO8" t="n">
-        <v>31188.56091175667</v>
+        <v>31188.56091175668</v>
       </c>
       <c r="CP8" t="n">
         <v>0.5556889333161329</v>
@@ -3842,7 +3842,7 @@
         <v>47649.45191889581</v>
       </c>
       <c r="DN8" t="n">
-        <v>39898.82459652367</v>
+        <v>39898.82459652366</v>
       </c>
       <c r="DO8" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         <v>44214.32900790396</v>
       </c>
       <c r="DS8" t="n">
-        <v>37022.4564333295</v>
+        <v>37022.45643332949</v>
       </c>
       <c r="DU8" t="n">
-        <v>21134.33703645748</v>
+        <v>21134.33703645747</v>
       </c>
       <c r="DV8" t="n">
-        <v>37022.4564333295</v>
+        <v>37022.45643332949</v>
       </c>
       <c r="DW8" t="n">
         <v>0.5708518308210169</v>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.505</v>
+        <v>0.5050000000000001</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="EH8" t="n">
-        <v>21134.33703645748</v>
+        <v>21134.33703645747</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
@@ -3944,13 +3944,13 @@
         <v>51737.38165059571</v>
       </c>
       <c r="EZ8" t="n">
-        <v>43321.81446859244</v>
+        <v>43321.81446859243</v>
       </c>
       <c r="FB8" t="n">
         <v>25352.82782038191</v>
       </c>
       <c r="FC8" t="n">
-        <v>43321.81446859244</v>
+        <v>43321.81446859243</v>
       </c>
       <c r="FD8" t="n">
         <v>0.5852208207659969</v>
@@ -4080,22 +4080,22 @@
         <v>4.246589507948345</v>
       </c>
       <c r="W9" t="n">
-        <v>5423.860800201263</v>
+        <v>5423.860800201262</v>
       </c>
       <c r="X9" t="n">
-        <v>4541.619304909007</v>
+        <v>4541.619304909006</v>
       </c>
       <c r="Z9" t="n">
         <v>2371.45141965701</v>
       </c>
       <c r="AA9" t="n">
-        <v>4541.619304909007</v>
+        <v>4541.619304909006</v>
       </c>
       <c r="AB9" t="n">
         <v>0.522159886253285</v>
       </c>
       <c r="AD9" t="n">
-        <v>2293.517748979049</v>
+        <v>2293.517748979048</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -4254,19 +4254,19 @@
         <v>6.435080300290991</v>
       </c>
       <c r="CK9" t="n">
-        <v>8143.232874289877</v>
+        <v>8143.232874289878</v>
       </c>
       <c r="CL9" t="n">
-        <v>6818.660173740484</v>
+        <v>6818.660173740485</v>
       </c>
       <c r="CN9" t="n">
-        <v>3789.053998591048</v>
+        <v>3789.053998591047</v>
       </c>
       <c r="CO9" t="n">
-        <v>6818.660173740484</v>
+        <v>6818.660173740485</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="CR9" t="n">
         <v>3443.423387738945</v>
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>3789.053998591048</v>
+        <v>3789.053998591047</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.555688933316133</v>
+        <v>0.5556889333161328</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4347,13 +4347,13 @@
         <v>8120.382434382784</v>
       </c>
       <c r="DU9" t="n">
-        <v>4635.535179634237</v>
+        <v>4635.535179634236</v>
       </c>
       <c r="DV9" t="n">
         <v>8120.382434382784</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.5708518308210166</v>
+        <v>0.5708518308210165</v>
       </c>
       <c r="DY9" t="n">
         <v>4100.793129363305</v>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>4635.535179634237</v>
+        <v>4635.535179634236</v>
       </c>
       <c r="EI9" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.5708518308210166</v>
+        <v>0.5708518308210165</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
@@ -4570,13 +4570,13 @@
         <v>3903.07942793573</v>
       </c>
       <c r="X10" t="n">
-        <v>3252.566189946442</v>
+        <v>3252.566189946441</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3252.566189946442</v>
+        <v>3252.566189946441</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -4741,7 +4741,7 @@
         <v>1.491189242174463</v>
       </c>
       <c r="CK10" t="n">
-        <v>5971.498577671163</v>
+        <v>5971.498577671164</v>
       </c>
       <c r="CL10" t="n">
         <v>4976.248814725969</v>
@@ -5054,7 +5054,7 @@
         <v>1.487890136805988</v>
       </c>
       <c r="W11" t="n">
-        <v>5854.619141903595</v>
+        <v>5854.619141903594</v>
       </c>
       <c r="X11" t="n">
         <v>4878.849284919662</v>
@@ -5231,13 +5231,13 @@
         <v>8957.247866506745</v>
       </c>
       <c r="CL11" t="n">
-        <v>7464.373222088954</v>
+        <v>7464.373222088955</v>
       </c>
       <c r="CN11" t="n">
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>7464.373222088954</v>
+        <v>7464.373222088955</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>0.7455946210872314</v>
       </c>
       <c r="CK12" t="n">
-        <v>2985.749288835581</v>
+        <v>2985.749288835582</v>
       </c>
       <c r="CL12" t="n">
         <v>2488.124407362985</v>
@@ -6518,13 +6518,13 @@
         <v>4369.826844688661</v>
       </c>
       <c r="X14" t="n">
-        <v>880.2223713363886</v>
+        <v>880.2223713363885</v>
       </c>
       <c r="Z14" t="n">
         <v>81.91190731983068</v>
       </c>
       <c r="AA14" t="n">
-        <v>880.2223713363886</v>
+        <v>880.2223713363885</v>
       </c>
       <c r="AB14" t="n">
         <v>0.0930581975500904</v>
@@ -6593,7 +6593,7 @@
         <v>866.1682521346527</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.009860828868239271</v>
+        <v>0.009860828868239274</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>827.6851576305363</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.009453091670496428</v>
+        <v>0.009453091670496433</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>4.145592880370348</v>
       </c>
       <c r="CK14" t="n">
-        <v>3875.658658845638</v>
+        <v>3875.658658845639</v>
       </c>
       <c r="CL14" t="n">
-        <v>780.6811520062807</v>
+        <v>780.6811520062809</v>
       </c>
       <c r="CN14" t="n">
         <v>77.31372058545385</v>
       </c>
       <c r="CO14" t="n">
-        <v>780.6811520062807</v>
+        <v>780.6811520062809</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.09903367128406329</v>
+        <v>0.09903367128406328</v>
       </c>
       <c r="CR14" t="n">
-        <v>70.26130368056526</v>
+        <v>70.26130368056528</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09903367128406329</v>
+        <v>0.09903367128406328</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6767,7 +6767,7 @@
         <v>789.890960813887</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.009016680229962243</v>
+        <v>0.009016680229962245</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
@@ -6782,7 +6782,7 @@
         <v>731.2798586021119</v>
       </c>
       <c r="DU14" t="n">
-        <v>74.3974656461376</v>
+        <v>74.39746564613759</v>
       </c>
       <c r="DV14" t="n">
         <v>731.2798586021119</v>
@@ -6815,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>74.3974656461376</v>
+        <v>74.39746564613759</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>0.009823365149089639</v>
       </c>
       <c r="R15" t="n">
-        <v>24109.89357210867</v>
+        <v>24109.89357210866</v>
       </c>
       <c r="S15" t="n">
         <v>20091.57797675722</v>
@@ -7002,7 +7002,7 @@
         <v>13.17431876104892</v>
       </c>
       <c r="W15" t="n">
-        <v>23467.14517553918</v>
+        <v>23467.14517553917</v>
       </c>
       <c r="X15" t="n">
         <v>19555.95431294931</v>
@@ -7176,7 +7176,7 @@
         <v>1.226486690749311</v>
       </c>
       <c r="CK15" t="n">
-        <v>2121.913501945821</v>
+        <v>2121.913501945822</v>
       </c>
       <c r="CL15" t="n">
         <v>1768.261251621518</v>
@@ -7492,13 +7492,13 @@
         <v>102432.5337835461</v>
       </c>
       <c r="X16" t="n">
-        <v>85360.44481962177</v>
+        <v>85360.44481962176</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>85360.44481962177</v>
+        <v>85360.44481962176</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -7666,13 +7666,13 @@
         <v>9262.011840297662</v>
       </c>
       <c r="CL16" t="n">
-        <v>7718.34320024805</v>
+        <v>7718.343200248051</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>7718.34320024805</v>
+        <v>7718.343200248051</v>
       </c>
       <c r="CP16" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="CO17" t="n">
-        <v>140.7978276408477</v>
+        <v>140.7978276408476</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>5.24860479052105</v>
       </c>
       <c r="W18" t="n">
-        <v>3223.458934916976</v>
+        <v>3223.458934916975</v>
       </c>
       <c r="X18" t="n">
         <v>2762.760839480125</v>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.009900251437879298</v>
+        <v>0.009900251437879299</v>
       </c>
       <c r="AV18" t="n">
         <v>3.513373476302835</v>
@@ -8950,7 +8950,7 @@
         <v>2.9992027374406</v>
       </c>
       <c r="W19" t="n">
-        <v>1982.850518560806</v>
+        <v>1982.850518560805</v>
       </c>
       <c r="X19" t="n">
         <v>1699.449192359052</v>
@@ -8965,7 +8965,7 @@
         <v>0.5904110454196356</v>
       </c>
       <c r="AD19" t="n">
-        <v>954.1316220331538</v>
+        <v>954.1316220331536</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -8974,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>17.07089659053906</v>
+        <v>17.07089659053905</v>
       </c>
       <c r="AH19" t="n">
         <v>0.5614358030372756</v>
@@ -8989,7 +8989,7 @@
         <v>0.01004495848848678</v>
       </c>
       <c r="AM19" t="n">
-        <v>986.5529885772156</v>
+        <v>986.5529885772154</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         <v>0.1425090630171998</v>
       </c>
       <c r="CK19" t="n">
-        <v>101.1042362864608</v>
+        <v>101.1042362864609</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>3.000621505671166</v>
       </c>
       <c r="W20" t="n">
-        <v>4602.46090508153</v>
+        <v>4602.460905081529</v>
       </c>
       <c r="X20" t="n">
         <v>3835.384087567941</v>
@@ -9611,16 +9611,16 @@
         <v>2.984340153459401</v>
       </c>
       <c r="CK20" t="n">
-        <v>4529.594366964615</v>
+        <v>4529.594366964616</v>
       </c>
       <c r="CL20" t="n">
-        <v>3774.661972470512</v>
+        <v>3774.661972470513</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>3774.661972470512</v>
+        <v>3774.661972470513</v>
       </c>
       <c r="CP20" t="n">
         <v>0</v>
@@ -9927,13 +9927,13 @@
         <v>3704.168081520535</v>
       </c>
       <c r="X21" t="n">
-        <v>3086.806734600446</v>
+        <v>3086.806734600445</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3086.806734600446</v>
+        <v>3086.806734600445</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -10098,16 +10098,16 @@
         <v>4.070515566251212</v>
       </c>
       <c r="CK21" t="n">
-        <v>3622.375812671442</v>
+        <v>3622.375812671443</v>
       </c>
       <c r="CL21" t="n">
-        <v>3018.646510559535</v>
+        <v>3018.646510559536</v>
       </c>
       <c r="CN21" t="n">
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>3018.646510559535</v>
+        <v>3018.646510559536</v>
       </c>
       <c r="CP21" t="n">
         <v>0</v>
@@ -10411,7 +10411,7 @@
         <v>1.000207168557055</v>
       </c>
       <c r="W22" t="n">
-        <v>2292.033612981765</v>
+        <v>2292.033612981764</v>
       </c>
       <c r="X22" t="n">
         <v>1910.028010818137</v>
@@ -10898,16 +10898,16 @@
         <v>6.112389654077718</v>
       </c>
       <c r="W23" t="n">
-        <v>4701.304050629933</v>
+        <v>4701.304050629932</v>
       </c>
       <c r="X23" t="n">
-        <v>3917.753375524945</v>
+        <v>3917.753375524944</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3917.753375524945</v>
+        <v>3917.753375524944</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -11072,16 +11072,16 @@
         <v>5.289491766490077</v>
       </c>
       <c r="CK23" t="n">
-        <v>4139.217350296696</v>
+        <v>4139.217350296697</v>
       </c>
       <c r="CL23" t="n">
-        <v>3449.347791913914</v>
+        <v>3449.347791913915</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>3449.347791913914</v>
+        <v>3449.347791913915</v>
       </c>
       <c r="CP23" t="n">
         <v>0</v>
@@ -11385,22 +11385,22 @@
         <v>1.815925773744298</v>
       </c>
       <c r="W24" t="n">
-        <v>962.8210235681215</v>
+        <v>962.8210235681214</v>
       </c>
       <c r="X24" t="n">
-        <v>822.869279953681</v>
+        <v>822.8692799536809</v>
       </c>
       <c r="Z24" t="n">
-        <v>553.0397311965521</v>
+        <v>553.039731196552</v>
       </c>
       <c r="AA24" t="n">
-        <v>822.869279953681</v>
+        <v>822.8692799536809</v>
       </c>
       <c r="AB24" t="n">
         <v>0.6720869823062084</v>
       </c>
       <c r="AD24" t="n">
-        <v>534.8650319698927</v>
+        <v>534.8650319698926</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>553.0397311965521</v>
+        <v>553.039731196552</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -11463,7 +11463,7 @@
         <v>841.3395471617433</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.003944331547295708</v>
+        <v>0.003944331547295709</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
         <v>831.5997002310124</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.003781236668198571</v>
+        <v>0.003781236668198574</v>
       </c>
       <c r="CI24" t="n">
         <v>0</v>
@@ -11559,22 +11559,22 @@
         <v>1.658237152148139</v>
       </c>
       <c r="CK24" t="n">
-        <v>917.7778384756582</v>
+        <v>917.7778384756583</v>
       </c>
       <c r="CL24" t="n">
-        <v>784.3733888414392</v>
+        <v>784.3733888414394</v>
       </c>
       <c r="CN24" t="n">
         <v>561.0177181157601</v>
       </c>
       <c r="CO24" t="n">
-        <v>784.3733888414392</v>
+        <v>784.3733888414394</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.7152431814960127</v>
+        <v>0.7152431814960126</v>
       </c>
       <c r="CR24" t="n">
-        <v>509.8427027469355</v>
+        <v>509.8427027469356</v>
       </c>
       <c r="CS24" t="n">
         <v>0</v>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.7152431814960127</v>
+        <v>0.7152431814960126</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11637,7 +11637,7 @@
         <v>815.4626020535411</v>
       </c>
       <c r="DO24" t="n">
-        <v>0.003606672091984897</v>
+        <v>0.003606672091984898</v>
       </c>
       <c r="DP24" t="n">
         <v>0</v>
@@ -11652,13 +11652,13 @@
         <v>754.9540454426475</v>
       </c>
       <c r="DU24" t="n">
-        <v>554.7098700343258</v>
+        <v>554.7098700343257</v>
       </c>
       <c r="DV24" t="n">
         <v>754.9540454426475</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.7347597822448733</v>
+        <v>0.7347597822448731</v>
       </c>
       <c r="DY24" t="n">
         <v>490.7201295377209</v>
@@ -11685,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="EH24" t="n">
-        <v>554.7098700343258</v>
+        <v>554.7098700343257</v>
       </c>
       <c r="EI24" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="EL24" t="n">
-        <v>0.7347597822448733</v>
+        <v>0.7347597822448731</v>
       </c>
       <c r="EM24" t="n">
         <v>0</v>
@@ -12533,16 +12533,16 @@
         <v>1.135327724411275</v>
       </c>
       <c r="CK26" t="n">
-        <v>5496.068571068576</v>
+        <v>5496.068571068577</v>
       </c>
       <c r="CL26" t="n">
-        <v>4645.776771793425</v>
+        <v>4645.776771793426</v>
       </c>
       <c r="CN26" t="n">
         <v>1840.353318707707</v>
       </c>
       <c r="CO26" t="n">
-        <v>4645.776771793425</v>
+        <v>4645.776771793426</v>
       </c>
       <c r="CP26" t="n">
         <v>0.3961346851362532</v>
@@ -12626,13 +12626,13 @@
         <v>4832.870830013078</v>
       </c>
       <c r="DU26" t="n">
-        <v>1966.707204190898</v>
+        <v>1966.707204190897</v>
       </c>
       <c r="DV26" t="n">
         <v>4832.870830013078</v>
       </c>
       <c r="DW26" t="n">
-        <v>0.4069438793971606</v>
+        <v>0.4069438793971605</v>
       </c>
       <c r="DY26" t="n">
         <v>1739.833498804708</v>
@@ -12659,7 +12659,7 @@
         <v>0</v>
       </c>
       <c r="EH26" t="n">
-        <v>1966.707204190898</v>
+        <v>1966.707204190897</v>
       </c>
       <c r="EI26" t="n">
         <v>0</v>
@@ -12671,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="EL26" t="n">
-        <v>0.4069438793971606</v>
+        <v>0.4069438793971605</v>
       </c>
       <c r="EM26" t="n">
         <v>0</v>
@@ -12849,19 +12849,19 @@
         <v>2785.322326859446</v>
       </c>
       <c r="X27" t="n">
-        <v>2362.859484014148</v>
+        <v>2362.859484014147</v>
       </c>
       <c r="Z27" t="n">
-        <v>902.7436977431026</v>
+        <v>902.7436977431025</v>
       </c>
       <c r="AA27" t="n">
-        <v>2362.859484014148</v>
+        <v>2362.859484014147</v>
       </c>
       <c r="AB27" t="n">
         <v>0.38205559994176</v>
       </c>
       <c r="AD27" t="n">
-        <v>873.0765793432275</v>
+        <v>873.0765793432274</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>902.7436977431026</v>
+        <v>902.7436977431025</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -13026,7 +13026,7 @@
         <v>2945.317480601845</v>
       </c>
       <c r="CN27" t="n">
-        <v>1197.531448697967</v>
+        <v>1197.531448697966</v>
       </c>
       <c r="CO27" t="n">
         <v>2945.317480601845</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="DA27" t="n">
-        <v>1197.531448697967</v>
+        <v>1197.531448697966</v>
       </c>
       <c r="DB27" t="n">
         <v>0</v>
@@ -13119,7 +13119,7 @@
         <v>3232.837039603607</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.4176826762145857</v>
+        <v>0.4176826762145856</v>
       </c>
       <c r="DY27" t="n">
         <v>1194.533286133533</v>
@@ -13158,7 +13158,7 @@
         <v>0</v>
       </c>
       <c r="EL27" t="n">
-        <v>0.4176826762145857</v>
+        <v>0.4176826762145856</v>
       </c>
       <c r="EM27" t="n">
         <v>0</v>
@@ -13336,13 +13336,13 @@
         <v>56.28609188220737</v>
       </c>
       <c r="X28" t="n">
-        <v>46.90507656850615</v>
+        <v>46.90507656850614</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>46.90507656850615</v>
+        <v>46.90507656850614</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -13820,16 +13820,16 @@
         <v>1.000207168557055</v>
       </c>
       <c r="W29" t="n">
-        <v>370.4890829719768</v>
+        <v>370.4890829719767</v>
       </c>
       <c r="X29" t="n">
-        <v>308.7409024766473</v>
+        <v>308.7409024766472</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>308.7409024766473</v>
+        <v>308.7409024766472</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -13994,7 +13994,7 @@
         <v>0.9947800511531335</v>
       </c>
       <c r="CK29" t="n">
-        <v>375.0034885384689</v>
+        <v>375.003488538469</v>
       </c>
       <c r="CL29" t="n">
         <v>312.5029071153908</v>
@@ -14394,16 +14394,16 @@
         <v>2.155992992460939</v>
       </c>
       <c r="BD30" t="n">
-        <v>67118.92312233742</v>
+        <v>67118.92312233741</v>
       </c>
       <c r="BE30" t="n">
-        <v>55932.43593528119</v>
+        <v>55932.43593528117</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>55932.43593528119</v>
+        <v>55932.43593528117</v>
       </c>
       <c r="BI30" t="n">
         <v>0</v>
@@ -14481,16 +14481,16 @@
         <v>2.143372636621241</v>
       </c>
       <c r="CK30" t="n">
-        <v>68325.23961409378</v>
+        <v>68325.23961409376</v>
       </c>
       <c r="CL30" t="n">
-        <v>56937.69967841149</v>
+        <v>56937.69967841148</v>
       </c>
       <c r="CN30" t="n">
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>56937.69967841149</v>
+        <v>56937.69967841148</v>
       </c>
       <c r="CP30" t="n">
         <v>0</v>
@@ -14568,16 +14568,16 @@
         <v>2.230469450704064</v>
       </c>
       <c r="DR30" t="n">
-        <v>72787.26105608784</v>
+        <v>72787.26105608782</v>
       </c>
       <c r="DS30" t="n">
-        <v>60656.05088007321</v>
+        <v>60656.05088007319</v>
       </c>
       <c r="DU30" t="n">
         <v>0</v>
       </c>
       <c r="DV30" t="n">
-        <v>60656.05088007321</v>
+        <v>60656.05088007319</v>
       </c>
       <c r="DW30" t="n">
         <v>0</v>
@@ -14655,16 +14655,16 @@
         <v>2.349219644259549</v>
       </c>
       <c r="EY30" t="n">
-        <v>78531.98543018253</v>
+        <v>78531.98543018251</v>
       </c>
       <c r="EZ30" t="n">
-        <v>65443.32119181878</v>
+        <v>65443.32119181877</v>
       </c>
       <c r="FB30" t="n">
         <v>0</v>
       </c>
       <c r="FC30" t="n">
-        <v>65443.32119181878</v>
+        <v>65443.32119181877</v>
       </c>
       <c r="FD30" t="n">
         <v>0</v>
@@ -14794,7 +14794,7 @@
         <v>1.000207168557055</v>
       </c>
       <c r="W31" t="n">
-        <v>395.1574089133304</v>
+        <v>395.1574089133303</v>
       </c>
       <c r="X31" t="n">
         <v>329.2978407611086</v>
@@ -14968,7 +14968,7 @@
         <v>0.9947800511531335</v>
       </c>
       <c r="CK31" t="n">
-        <v>420.8415152261001</v>
+        <v>420.8415152261002</v>
       </c>
       <c r="CL31" t="n">
         <v>350.7012626884168</v>
@@ -15284,13 +15284,13 @@
         <v>5926.843250012158</v>
       </c>
       <c r="X32" t="n">
-        <v>4939.036041676799</v>
+        <v>4939.036041676798</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4939.036041676799</v>
+        <v>4939.036041676798</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -15455,16 +15455,16 @@
         <v>5.874973480590525</v>
       </c>
       <c r="CK32" t="n">
-        <v>6788.283433894876</v>
+        <v>6788.283433894877</v>
       </c>
       <c r="CL32" t="n">
-        <v>5656.902861579063</v>
+        <v>5656.902861579064</v>
       </c>
       <c r="CN32" t="n">
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>5656.902861579063</v>
+        <v>5656.902861579064</v>
       </c>
       <c r="CP32" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>3051.666801151243</v>
       </c>
       <c r="Z33" t="n">
-        <v>788.840588996069</v>
+        <v>788.8405889960688</v>
       </c>
       <c r="AA33" t="n">
         <v>3051.666801151243</v>
@@ -15783,7 +15783,7 @@
         <v>0.2584949931946955</v>
       </c>
       <c r="AD33" t="n">
-        <v>762.9167002878108</v>
+        <v>762.9167002878107</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>788.840588996069</v>
+        <v>788.8405889960688</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -15954,10 +15954,10 @@
         <v>3088.85132892109</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.2750935313446203</v>
+        <v>0.2750935313446202</v>
       </c>
       <c r="CR33" t="n">
-        <v>772.2128322302725</v>
+        <v>772.2128322302726</v>
       </c>
       <c r="CS33" t="n">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.2750935313446203</v>
+        <v>0.2750935313446202</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16035,13 +16035,13 @@
         <v>3075.401131764765</v>
       </c>
       <c r="DU33" t="n">
-        <v>869.1081022658136</v>
+        <v>869.1081022658135</v>
       </c>
       <c r="DV33" t="n">
         <v>3075.401131764765</v>
       </c>
       <c r="DW33" t="n">
-        <v>0.2825999162480282</v>
+        <v>0.2825999162480281</v>
       </c>
       <c r="DY33" t="n">
         <v>768.8502829411913</v>
@@ -16068,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="EH33" t="n">
-        <v>869.1081022658136</v>
+        <v>869.1081022658135</v>
       </c>
       <c r="EI33" t="n">
         <v>0</v>
@@ -16080,7 +16080,7 @@
         <v>0</v>
       </c>
       <c r="EL33" t="n">
-        <v>0.2825999162480282</v>
+        <v>0.2825999162480281</v>
       </c>
       <c r="EM33" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>1.016102770203479</v>
       </c>
       <c r="W34" t="n">
-        <v>723.1137558534579</v>
+        <v>723.1137558534577</v>
       </c>
       <c r="X34" t="n">
         <v>602.5947965445482</v>
@@ -16432,13 +16432,13 @@
         <v>775.4921936177836</v>
       </c>
       <c r="CL34" t="n">
-        <v>646.2434946814864</v>
+        <v>646.2434946814865</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>646.2434946814864</v>
+        <v>646.2434946814865</v>
       </c>
       <c r="CP34" t="n">
         <v>0</v>
@@ -16751,7 +16751,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1234.564708822714</v>
+        <v>1234.564708822713</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -17899,7 +17899,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>638.0248814408791</v>
+        <v>638.0248814408792</v>
       </c>
       <c r="CP37" t="n">
         <v>0</v>
@@ -18212,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2547.518861541422</v>
+        <v>2547.518861541421</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -18873,7 +18873,7 @@
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>1914.410225438387</v>
+        <v>1914.410225438388</v>
       </c>
       <c r="CP39" t="n">
         <v>0</v>
@@ -20160,7 +20160,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>587.9877467557695</v>
+        <v>587.9877467557694</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>589.2584397943386</v>
+        <v>589.2584397943388</v>
       </c>
       <c r="CP42" t="n">
         <v>0</v>
@@ -20647,7 +20647,7 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>382.0829536646707</v>
+        <v>382.0829536646706</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1684.350013215212</v>
+        <v>1684.350013215211</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -21612,16 +21612,16 @@
         <v>0.2058331191918632</v>
       </c>
       <c r="W45" t="n">
-        <v>524.8446814027309</v>
+        <v>524.8446814027308</v>
       </c>
       <c r="X45" t="n">
-        <v>437.3705678356091</v>
+        <v>437.370567835609</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>437.3705678356091</v>
+        <v>437.370567835609</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -22586,16 +22586,16 @@
         <v>0.2744441589224842</v>
       </c>
       <c r="W47" t="n">
-        <v>699.7929085369746</v>
+        <v>699.7929085369744</v>
       </c>
       <c r="X47" t="n">
-        <v>583.1607571141456</v>
+        <v>583.1607571141454</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>583.1607571141456</v>
+        <v>583.1607571141454</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.1186164704785137</v>
       </c>
       <c r="CK47" t="n">
-        <v>308.6320452120193</v>
+        <v>308.6320452120194</v>
       </c>
       <c r="CL47" t="n">
         <v>257.1933710100161</v>
@@ -23079,7 +23079,7 @@
         <v>1930.068240464078</v>
       </c>
       <c r="Z48" t="n">
-        <v>1157.478105907019</v>
+        <v>1157.478105907018</v>
       </c>
       <c r="AA48" t="n">
         <v>1930.068240464078</v>
@@ -23112,7 +23112,7 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1157.478105907019</v>
+        <v>1157.478105907018</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -23250,16 +23250,16 @@
         <v>2166.314867377661</v>
       </c>
       <c r="CL48" t="n">
-        <v>1839.620018603782</v>
+        <v>1839.620018603783</v>
       </c>
       <c r="CN48" t="n">
         <v>1174.076756019932</v>
       </c>
       <c r="CO48" t="n">
-        <v>1839.620018603782</v>
+        <v>1839.620018603783</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.6382169927195189</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="CR48" t="n">
         <v>1066.979610790194</v>
@@ -23298,7 +23298,7 @@
         <v>0</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.6382169927195189</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="DF48" t="n">
         <v>0</v>
@@ -23346,7 +23346,7 @@
         <v>737.6008905490961</v>
       </c>
       <c r="DW48" t="n">
-        <v>0.4037307395800887</v>
+        <v>0.4037307395800886</v>
       </c>
       <c r="DY48" t="n">
         <v>263.4397039195836</v>
@@ -23385,7 +23385,7 @@
         <v>0</v>
       </c>
       <c r="EL48" t="n">
-        <v>0.4037307395800887</v>
+        <v>0.4037307395800886</v>
       </c>
       <c r="EM48" t="n">
         <v>0</v>
@@ -23560,7 +23560,7 @@
         <v>3.640043398490274</v>
       </c>
       <c r="W49" t="n">
-        <v>7449.94270101808</v>
+        <v>7449.942701018079</v>
       </c>
       <c r="X49" t="n">
         <v>1365.897833894915</v>
@@ -23734,13 +23734,13 @@
         <v>3.324036777632676</v>
       </c>
       <c r="CK49" t="n">
-        <v>6607.618111069729</v>
+        <v>6607.61811106973</v>
       </c>
       <c r="CL49" t="n">
         <v>1211.463178620366</v>
       </c>
       <c r="CN49" t="n">
-        <v>466.5719574609168</v>
+        <v>466.5719574609167</v>
       </c>
       <c r="CO49" t="n">
         <v>1211.463178620366</v>
@@ -23773,7 +23773,7 @@
         <v>0</v>
       </c>
       <c r="DA49" t="n">
-        <v>466.5719574609168</v>
+        <v>466.5719574609167</v>
       </c>
       <c r="DB49" t="n">
         <v>0</v>
@@ -23827,13 +23827,13 @@
         <v>1134.800749240619</v>
       </c>
       <c r="DU49" t="n">
-        <v>448.9724353710379</v>
+        <v>448.9724353710378</v>
       </c>
       <c r="DV49" t="n">
         <v>1134.800749240619</v>
       </c>
       <c r="DW49" t="n">
-        <v>0.3956398827472395</v>
+        <v>0.3956398827472394</v>
       </c>
       <c r="DY49" t="n">
         <v>397.1802622342166</v>
@@ -23860,7 +23860,7 @@
         <v>0</v>
       </c>
       <c r="EH49" t="n">
-        <v>448.9724353710379</v>
+        <v>448.9724353710378</v>
       </c>
       <c r="EI49" t="n">
         <v>0</v>
@@ -23872,7 +23872,7 @@
         <v>0</v>
       </c>
       <c r="EL49" t="n">
-        <v>0.3956398827472395</v>
+        <v>0.3956398827472394</v>
       </c>
       <c r="EM49" t="n">
         <v>0</v>
@@ -24230,7 +24230,7 @@
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>63.54948889784939</v>
+        <v>63.5494888978494</v>
       </c>
       <c r="CP50" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>21.18316296594979</v>
+        <v>21.1831629659498</v>
       </c>
       <c r="CP51" t="n">
         <v>0</v>
@@ -25508,13 +25508,13 @@
         <v>2.115402497398194</v>
       </c>
       <c r="W53" t="n">
-        <v>7636.189352054293</v>
+        <v>7636.189352054292</v>
       </c>
       <c r="X53" t="n">
         <v>1610.382318498426</v>
       </c>
       <c r="Z53" t="n">
-        <v>815.900502263773</v>
+        <v>815.9005022637729</v>
       </c>
       <c r="AA53" t="n">
         <v>1610.382318498426</v>
@@ -25523,7 +25523,7 @@
         <v>0.5066501866616032</v>
       </c>
       <c r="AD53" t="n">
-        <v>789.0873360642288</v>
+        <v>789.0873360642287</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>815.900502263773</v>
+        <v>815.9005022637729</v>
       </c>
       <c r="AN53" t="n">
         <v>0</v>
@@ -25682,7 +25682,7 @@
         <v>1.953877698380296</v>
       </c>
       <c r="CK53" t="n">
-        <v>7205.945821711521</v>
+        <v>7205.945821711522</v>
       </c>
       <c r="CL53" t="n">
         <v>0</v>
@@ -25998,13 +25998,13 @@
         <v>155742.5793112252</v>
       </c>
       <c r="X54" t="n">
-        <v>32446.45086273166</v>
+        <v>32446.45086273165</v>
       </c>
       <c r="Z54" t="n">
-        <v>736.064767527287</v>
+        <v>736.0647675272869</v>
       </c>
       <c r="AA54" t="n">
-        <v>32446.45086273166</v>
+        <v>32446.45086273165</v>
       </c>
       <c r="AB54" t="n">
         <v>0.02268552485574744</v>
@@ -26013,7 +26013,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>736.064767527287</v>
+        <v>736.0647675272869</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -26037,7 +26037,7 @@
         <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>736.064767527287</v>
+        <v>736.0647675272869</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
@@ -26482,16 +26482,16 @@
         <v>103.8942571596645</v>
       </c>
       <c r="W55" t="n">
-        <v>142052.7724937305</v>
+        <v>142052.7724937304</v>
       </c>
       <c r="X55" t="n">
-        <v>29594.40072853873</v>
+        <v>29594.40072853872</v>
       </c>
       <c r="Z55" t="n">
-        <v>671.3645133182156</v>
+        <v>671.3645133182155</v>
       </c>
       <c r="AA55" t="n">
-        <v>29594.40072853873</v>
+        <v>29594.40072853872</v>
       </c>
       <c r="AB55" t="n">
         <v>0.02268552485574744</v>
@@ -26500,7 +26500,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>671.3645133182156</v>
+        <v>671.3645133182155</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -26524,7 +26524,7 @@
         <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>671.3645133182156</v>
+        <v>671.3645133182155</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -27143,7 +27143,7 @@
         <v>434.6268005574108</v>
       </c>
       <c r="CK56" t="n">
-        <v>610431.7906466608</v>
+        <v>610431.790646661</v>
       </c>
       <c r="CL56" t="n">
         <v>0</v>
@@ -27949,7 +27949,7 @@
         <v>28029.56510898356</v>
       </c>
       <c r="Z58" t="n">
-        <v>635.8653959756377</v>
+        <v>635.8653959756376</v>
       </c>
       <c r="AA58" t="n">
         <v>28029.56510898356</v>
@@ -27961,7 +27961,7 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>635.8653959756377</v>
+        <v>635.8653959756376</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -27985,7 +27985,7 @@
         <v>0</v>
       </c>
       <c r="AN58" t="n">
-        <v>635.8653959756377</v>
+        <v>635.8653959756376</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -28430,7 +28430,7 @@
         <v>0.2243285150398349</v>
       </c>
       <c r="W59" t="n">
-        <v>816.7345668934855</v>
+        <v>816.7345668934854</v>
       </c>
       <c r="X59" t="n">
         <v>172.239692442659</v>
@@ -28604,7 +28604,7 @@
         <v>0.2071995675462213</v>
       </c>
       <c r="CK59" t="n">
-        <v>770.7175357261408</v>
+        <v>770.7175357261409</v>
       </c>
       <c r="CL59" t="n">
         <v>0</v>
@@ -29091,7 +29091,7 @@
         <v>0.9536154961372597</v>
       </c>
       <c r="CK60" t="n">
-        <v>2070.598421983355</v>
+        <v>2070.598421983356</v>
       </c>
       <c r="CL60" t="n">
         <v>1725.49868498613</v>
@@ -29407,13 +29407,13 @@
         <v>688.9978789007459</v>
       </c>
       <c r="X61" t="n">
-        <v>473.1110152347554</v>
+        <v>473.1110152347553</v>
       </c>
       <c r="Z61" t="n">
         <v>313.0798813784156</v>
       </c>
       <c r="AA61" t="n">
-        <v>473.1110152347554</v>
+        <v>473.1110152347553</v>
       </c>
       <c r="AB61" t="n">
         <v>0.6617471825784206</v>
@@ -29581,16 +29581,16 @@
         <v>297.9548976101561</v>
       </c>
       <c r="CL61" t="n">
-        <v>204.5953237583412</v>
+        <v>204.5953237583413</v>
       </c>
       <c r="CN61" t="n">
-        <v>88.72537641924032</v>
+        <v>88.72537641924029</v>
       </c>
       <c r="CO61" t="n">
-        <v>204.5953237583412</v>
+        <v>204.5953237583413</v>
       </c>
       <c r="CP61" t="n">
-        <v>0.4336627777672902</v>
+        <v>0.43366277776729</v>
       </c>
       <c r="CR61" t="n">
         <v>80.63200903485678</v>
@@ -29617,7 +29617,7 @@
         <v>0</v>
       </c>
       <c r="DA61" t="n">
-        <v>88.72537641924032</v>
+        <v>88.72537641924029</v>
       </c>
       <c r="DB61" t="n">
         <v>0</v>
@@ -29629,7 +29629,7 @@
         <v>0</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.4336627777672902</v>
+        <v>0.43366277776729</v>
       </c>
       <c r="DF61" t="n">
         <v>0</v>
@@ -29897,16 +29897,16 @@
         <v>813.8172970458128</v>
       </c>
       <c r="Z62" t="n">
-        <v>555.3707191865789</v>
+        <v>555.3707191865788</v>
       </c>
       <c r="AA62" t="n">
         <v>813.8172970458128</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.6824267820339963</v>
+        <v>0.6824267820339961</v>
       </c>
       <c r="AD62" t="n">
-        <v>537.1194160502365</v>
+        <v>537.1194160502364</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -29918,7 +29918,7 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.6600000000000001</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -29930,7 +29930,7 @@
         <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>555.3707191865789</v>
+        <v>555.3707191865788</v>
       </c>
       <c r="AN62" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
         <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.6824267820339963</v>
+        <v>0.6824267820339961</v>
       </c>
       <c r="AR62" t="n">
         <v>0</v>
@@ -30044,7 +30044,7 @@
         <v>281.6747135764824</v>
       </c>
       <c r="CD62" t="n">
-        <v>3.531067230657479</v>
+        <v>3.53106723065748</v>
       </c>
       <c r="CE62" t="n">
         <v>0.001279367721323851</v>
@@ -30062,7 +30062,7 @@
         <v>0</v>
       </c>
       <c r="CJ62" t="n">
-        <v>3.531067230657479</v>
+        <v>3.53106723065748</v>
       </c>
       <c r="CK62" t="n">
         <v>2168.707265068756</v>
@@ -30378,22 +30378,22 @@
         <v>2.633410079228952</v>
       </c>
       <c r="W63" t="n">
-        <v>1985.128674047418</v>
+        <v>1985.128674047417</v>
       </c>
       <c r="X63" t="n">
-        <v>1663.940128693056</v>
+        <v>1663.940128693055</v>
       </c>
       <c r="Z63" t="n">
-        <v>911.8548075549315</v>
+        <v>911.8548075549314</v>
       </c>
       <c r="AA63" t="n">
-        <v>1663.940128693056</v>
+        <v>1663.940128693055</v>
       </c>
       <c r="AB63" t="n">
         <v>0.5480093855727546</v>
       </c>
       <c r="AD63" t="n">
-        <v>881.8882682073195</v>
+        <v>881.8882682073194</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -30417,7 +30417,7 @@
         <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>911.8548075549315</v>
+        <v>911.8548075549314</v>
       </c>
       <c r="AN63" t="n">
         <v>0</v>
@@ -30555,19 +30555,19 @@
         <v>1690.68677300571</v>
       </c>
       <c r="CL63" t="n">
-        <v>1417.138144964183</v>
+        <v>1417.138144964184</v>
       </c>
       <c r="CN63" t="n">
         <v>826.4725378068866</v>
       </c>
       <c r="CO63" t="n">
-        <v>1417.138144964183</v>
+        <v>1417.138144964184</v>
       </c>
       <c r="CP63" t="n">
-        <v>0.583198286450595</v>
+        <v>0.5831982864505949</v>
       </c>
       <c r="CR63" t="n">
-        <v>751.0832168310172</v>
+        <v>751.0832168310174</v>
       </c>
       <c r="CS63" t="n">
         <v>0</v>
@@ -30603,7 +30603,7 @@
         <v>0</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.583198286450595</v>
+        <v>0.5831982864505949</v>
       </c>
       <c r="DF63" t="n">
         <v>0</v>
@@ -30645,13 +30645,13 @@
         <v>1319.444874570264</v>
       </c>
       <c r="DU63" t="n">
-        <v>783.8793044679849</v>
+        <v>783.8793044679848</v>
       </c>
       <c r="DV63" t="n">
         <v>1319.444874570264</v>
       </c>
       <c r="DW63" t="n">
-        <v>0.5940978055057359</v>
+        <v>0.5940978055057358</v>
       </c>
       <c r="DY63" t="n">
         <v>693.4532349436378</v>
@@ -30678,7 +30678,7 @@
         <v>0</v>
       </c>
       <c r="EH63" t="n">
-        <v>783.8793044679849</v>
+        <v>783.8793044679848</v>
       </c>
       <c r="EI63" t="n">
         <v>0</v>
@@ -30690,7 +30690,7 @@
         <v>0</v>
       </c>
       <c r="EL63" t="n">
-        <v>0.5940978055057359</v>
+        <v>0.5940978055057358</v>
       </c>
       <c r="EM63" t="n">
         <v>0</v>
@@ -30868,19 +30868,19 @@
         <v>1022.665677198399</v>
       </c>
       <c r="X64" t="n">
-        <v>857.2052531382348</v>
+        <v>857.2052531382346</v>
       </c>
       <c r="Z64" t="n">
-        <v>469.7565240820216</v>
+        <v>469.7565240820215</v>
       </c>
       <c r="AA64" t="n">
-        <v>857.2052531382348</v>
+        <v>857.2052531382346</v>
       </c>
       <c r="AB64" t="n">
         <v>0.5480093855727546</v>
       </c>
       <c r="AD64" t="n">
-        <v>454.3187841632645</v>
+        <v>454.3187841632644</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -30904,7 +30904,7 @@
         <v>0</v>
       </c>
       <c r="AM64" t="n">
-        <v>469.7565240820216</v>
+        <v>469.7565240820215</v>
       </c>
       <c r="AN64" t="n">
         <v>0</v>
@@ -31039,19 +31039,19 @@
         <v>0.8428458243436149</v>
       </c>
       <c r="CK64" t="n">
-        <v>871.0036986780541</v>
+        <v>871.0036986780542</v>
       </c>
       <c r="CL64" t="n">
         <v>730.0811620617369</v>
       </c>
       <c r="CN64" t="n">
-        <v>425.7820826842641</v>
+        <v>425.782082684264</v>
       </c>
       <c r="CO64" t="n">
         <v>730.0811620617369</v>
       </c>
       <c r="CP64" t="n">
-        <v>0.583198286450595</v>
+        <v>0.5831982864505949</v>
       </c>
       <c r="CR64" t="n">
         <v>386.9430158927206</v>
@@ -31078,7 +31078,7 @@
         <v>0</v>
       </c>
       <c r="DA64" t="n">
-        <v>425.7820826842641</v>
+        <v>425.782082684264</v>
       </c>
       <c r="DB64" t="n">
         <v>0</v>
@@ -31090,7 +31090,7 @@
         <v>0</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.583198286450595</v>
+        <v>0.5831982864505949</v>
       </c>
       <c r="DF64" t="n">
         <v>0</v>
@@ -31132,13 +31132,13 @@
         <v>679.7633476040706</v>
       </c>
       <c r="DU64" t="n">
-        <v>403.8459130748111</v>
+        <v>403.8459130748109</v>
       </c>
       <c r="DV64" t="n">
         <v>679.7633476040706</v>
       </c>
       <c r="DW64" t="n">
-        <v>0.5940978055057358</v>
+        <v>0.5940978055057357</v>
       </c>
       <c r="DY64" t="n">
         <v>357.2594061920824</v>
@@ -31165,7 +31165,7 @@
         <v>0</v>
       </c>
       <c r="EH64" t="n">
-        <v>403.8459130748111</v>
+        <v>403.8459130748109</v>
       </c>
       <c r="EI64" t="n">
         <v>0</v>
@@ -31177,7 +31177,7 @@
         <v>0</v>
       </c>
       <c r="EL64" t="n">
-        <v>0.5940978055057358</v>
+        <v>0.5940978055057357</v>
       </c>
       <c r="EM64" t="n">
         <v>0</v>
@@ -31355,19 +31355,19 @@
         <v>641.510355688665</v>
       </c>
       <c r="X65" t="n">
-        <v>133.6491394644793</v>
+        <v>133.6491394644792</v>
       </c>
       <c r="Z65" t="n">
-        <v>91.20575216635737</v>
+        <v>91.20575216635736</v>
       </c>
       <c r="AA65" t="n">
-        <v>133.6491394644793</v>
+        <v>133.6491394644792</v>
       </c>
       <c r="AB65" t="n">
         <v>0.6824267820339963</v>
       </c>
       <c r="AD65" t="n">
-        <v>88.20843204655633</v>
+        <v>88.20843204655631</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -31391,7 +31391,7 @@
         <v>0</v>
       </c>
       <c r="AM65" t="n">
-        <v>91.20575216635737</v>
+        <v>91.20575216635736</v>
       </c>
       <c r="AN65" t="n">
         <v>0</v>
@@ -31526,7 +31526,7 @@
         <v>0.4893578529518084</v>
       </c>
       <c r="CK65" t="n">
-        <v>683.3262586659538</v>
+        <v>683.3262586659539</v>
       </c>
       <c r="CL65" t="n">
         <v>0</v>
@@ -31842,16 +31842,16 @@
         <v>18967.2815088947</v>
       </c>
       <c r="X66" t="n">
-        <v>3999.999413111222</v>
+        <v>3999.999413111221</v>
       </c>
       <c r="Z66" t="n">
         <v>2274.755606356137</v>
       </c>
       <c r="AA66" t="n">
-        <v>3999.999413111222</v>
+        <v>3999.999413111221</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.5686889850283303</v>
+        <v>0.5686889850283302</v>
       </c>
       <c r="AD66" t="n">
         <v>2199.999677211172</v>
@@ -31890,7 +31890,7 @@
         <v>0</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.5686889850283303</v>
+        <v>0.5686889850283302</v>
       </c>
       <c r="AR66" t="n">
         <v>0</v>
@@ -32813,16 +32813,16 @@
         <v>0.1081375672739091</v>
       </c>
       <c r="W68" t="n">
-        <v>82.1969071011421</v>
+        <v>82.19690710114209</v>
       </c>
       <c r="X68" t="n">
-        <v>68.4974225842851</v>
+        <v>68.49742258428509</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>68.4974225842851</v>
+        <v>68.49742258428509</v>
       </c>
       <c r="AB68" t="n">
         <v>0</v>
@@ -32987,16 +32987,16 @@
         <v>0.1185955217470426</v>
       </c>
       <c r="CK68" t="n">
-        <v>87.55479082335397</v>
+        <v>87.55479082335398</v>
       </c>
       <c r="CL68" t="n">
-        <v>72.9623256861283</v>
+        <v>72.96232568612831</v>
       </c>
       <c r="CN68" t="n">
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>72.9623256861283</v>
+        <v>72.96232568612831</v>
       </c>
       <c r="CP68" t="n">
         <v>0</v>
@@ -33300,16 +33300,16 @@
         <v>4.992131962097584</v>
       </c>
       <c r="W69" t="n">
-        <v>9658.942990243981</v>
+        <v>9658.942990243979</v>
       </c>
       <c r="X69" t="n">
-        <v>8049.119158536651</v>
+        <v>8049.11915853665</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>8049.119158536651</v>
+        <v>8049.11915853665</v>
       </c>
       <c r="AB69" t="n">
         <v>0</v>
@@ -33474,16 +33474,16 @@
         <v>4.953388260715742</v>
       </c>
       <c r="CK69" t="n">
-        <v>9366.755531599156</v>
+        <v>9366.755531599158</v>
       </c>
       <c r="CL69" t="n">
-        <v>7805.629609665963</v>
+        <v>7805.629609665964</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>7805.629609665963</v>
+        <v>7805.629609665964</v>
       </c>
       <c r="CP69" t="n">
         <v>0</v>
@@ -34764,19 +34764,19 @@
         <v>10716.30885549913</v>
       </c>
       <c r="X72" t="n">
-        <v>9078.750506522649</v>
+        <v>9078.750506522647</v>
       </c>
       <c r="Z72" t="n">
-        <v>5444.602796927793</v>
+        <v>5444.602796927792</v>
       </c>
       <c r="AA72" t="n">
-        <v>9078.750506522649</v>
+        <v>9078.750506522647</v>
       </c>
       <c r="AB72" t="n">
         <v>0.5997083842116937</v>
       </c>
       <c r="AD72" t="n">
-        <v>5265.675293783136</v>
+        <v>5265.675293783135</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -34800,7 +34800,7 @@
         <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>5444.602796927793</v>
+        <v>5444.602796927792</v>
       </c>
       <c r="AN72" t="n">
         <v>0</v>
@@ -34947,10 +34947,10 @@
         <v>10217.98663198094</v>
       </c>
       <c r="CP72" t="n">
-        <v>0.638216992719519</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="CR72" t="n">
-        <v>5926.432246548944</v>
+        <v>5926.432246548945</v>
       </c>
       <c r="CS72" t="n">
         <v>0</v>
@@ -34986,7 +34986,7 @@
         <v>0</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.638216992719519</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="DF72" t="n">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         <v>10757.49181166077</v>
       </c>
       <c r="DU72" t="n">
-        <v>7052.953781232904</v>
+        <v>7052.953781232903</v>
       </c>
       <c r="DV72" t="n">
         <v>10757.49181166077</v>
       </c>
       <c r="DW72" t="n">
-        <v>0.6556318056954253</v>
+        <v>0.6556318056954252</v>
       </c>
       <c r="DY72" t="n">
         <v>6239.345250763247</v>
@@ -35061,7 +35061,7 @@
         <v>0</v>
       </c>
       <c r="EH72" t="n">
-        <v>7052.953781232904</v>
+        <v>7052.953781232903</v>
       </c>
       <c r="EI72" t="n">
         <v>0</v>
@@ -35073,7 +35073,7 @@
         <v>0</v>
       </c>
       <c r="EL72" t="n">
-        <v>0.6556318056954253</v>
+        <v>0.6556318056954252</v>
       </c>
       <c r="EM72" t="n">
         <v>0</v>
@@ -35422,7 +35422,7 @@
         <v>0.04878910408199253</v>
       </c>
       <c r="CK73" t="n">
-        <v>66.38622509251684</v>
+        <v>66.38622509251685</v>
       </c>
       <c r="CL73" t="n">
         <v>55.32185424376404</v>
@@ -35909,7 +35909,7 @@
         <v>0.1463673122459776</v>
       </c>
       <c r="CK74" t="n">
-        <v>298.7380129163258</v>
+        <v>298.7380129163259</v>
       </c>
       <c r="CL74" t="n">
         <v>248.9483440969382</v>
@@ -36399,13 +36399,13 @@
         <v>55.18903577944656</v>
       </c>
       <c r="CL75" t="n">
-        <v>45.9908631495388</v>
+        <v>45.99086314953881</v>
       </c>
       <c r="CN75" t="n">
         <v>0</v>
       </c>
       <c r="CO75" t="n">
-        <v>45.9908631495388</v>
+        <v>45.99086314953881</v>
       </c>
       <c r="CP75" t="n">
         <v>0</v>
@@ -36712,13 +36712,13 @@
         <v>1025.935556835879</v>
       </c>
       <c r="X76" t="n">
-        <v>854.9462973632325</v>
+        <v>854.9462973632324</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>854.9462973632325</v>
+        <v>854.9462973632324</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>0.09757820816398506</v>
       </c>
       <c r="CK76" t="n">
-        <v>220.756108847633</v>
+        <v>220.7561088476331</v>
       </c>
       <c r="CL76" t="n">
         <v>183.9634240396942</v>
@@ -37202,7 +37202,7 @@
         <v>119.656376167594</v>
       </c>
       <c r="Z77" t="n">
-        <v>62.7643210512681</v>
+        <v>62.76432105126809</v>
       </c>
       <c r="AA77" t="n">
         <v>119.656376167594</v>
@@ -37211,7 +37211,7 @@
         <v>0.5245380401906762</v>
       </c>
       <c r="AD77" t="n">
-        <v>60.70167962982044</v>
+        <v>60.70167962982043</v>
       </c>
       <c r="AE77" t="n">
         <v>0</v>
@@ -37235,7 +37235,7 @@
         <v>0</v>
       </c>
       <c r="AM77" t="n">
-        <v>62.7643210512681</v>
+        <v>62.76432105126809</v>
       </c>
       <c r="AN77" t="n">
         <v>0</v>
@@ -37382,10 +37382,10 @@
         <v>114.028660179636</v>
       </c>
       <c r="CP77" t="n">
-        <v>0.5582197938045034</v>
+        <v>0.5582197938045033</v>
       </c>
       <c r="CR77" t="n">
-        <v>57.84673930912933</v>
+        <v>57.84673930912934</v>
       </c>
       <c r="CS77" t="n">
         <v>0</v>
@@ -37421,7 +37421,7 @@
         <v>0</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.5582197938045034</v>
+        <v>0.5582197938045033</v>
       </c>
       <c r="DF77" t="n">
         <v>0</v>
@@ -37463,13 +37463,13 @@
         <v>110.5601684371724</v>
       </c>
       <c r="DU77" t="n">
-        <v>63.40092207617444</v>
+        <v>63.40092207617442</v>
       </c>
       <c r="DV77" t="n">
         <v>110.5601684371724</v>
       </c>
       <c r="DW77" t="n">
-        <v>0.5734517500504988</v>
+        <v>0.5734517500504986</v>
       </c>
       <c r="DY77" t="n">
         <v>56.08717344817757</v>
@@ -37496,7 +37496,7 @@
         <v>0</v>
       </c>
       <c r="EH77" t="n">
-        <v>63.40092207617444</v>
+        <v>63.40092207617442</v>
       </c>
       <c r="EI77" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>0</v>
       </c>
       <c r="EL77" t="n">
-        <v>0.5734517500504988</v>
+        <v>0.5734517500504986</v>
       </c>
       <c r="EM77" t="n">
         <v>0</v>
@@ -37683,19 +37683,19 @@
         <v>7.737843702710827</v>
       </c>
       <c r="W78" t="n">
-        <v>4570.680808324927</v>
+        <v>4570.680808324926</v>
       </c>
       <c r="X78" t="n">
-        <v>3860.100567272092</v>
+        <v>3860.100567272091</v>
       </c>
       <c r="Z78" t="n">
         <v>2594.323341656383</v>
       </c>
       <c r="AA78" t="n">
-        <v>3860.100567272092</v>
+        <v>3860.100567272091</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.6720869823062083</v>
+        <v>0.6720869823062084</v>
       </c>
       <c r="AD78" t="n">
         <v>2509.065368726859</v>
@@ -37734,7 +37734,7 @@
         <v>0</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.6720869823062083</v>
+        <v>0.6720869823062084</v>
       </c>
       <c r="AR78" t="n">
         <v>0</v>
@@ -37860,16 +37860,16 @@
         <v>5101.470459939239</v>
       </c>
       <c r="CL78" t="n">
-        <v>4308.371081276644</v>
+        <v>4308.371081276645</v>
       </c>
       <c r="CN78" t="n">
         <v>3081.533039237724</v>
       </c>
       <c r="CO78" t="n">
-        <v>4308.371081276644</v>
+        <v>4308.371081276645</v>
       </c>
       <c r="CP78" t="n">
-        <v>0.7152431814960128</v>
+        <v>0.7152431814960126</v>
       </c>
       <c r="CR78" t="n">
         <v>2800.441202829819</v>
@@ -37908,7 +37908,7 @@
         <v>0</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.7152431814960128</v>
+        <v>0.7152431814960126</v>
       </c>
       <c r="DF78" t="n">
         <v>0</v>
@@ -37956,7 +37956,7 @@
         <v>3439.765386738447</v>
       </c>
       <c r="DW78" t="n">
-        <v>0.6376194284157732</v>
+        <v>0.6376194284157731</v>
       </c>
       <c r="DY78" t="n">
         <v>1940.252910276502</v>
@@ -37995,7 +37995,7 @@
         <v>0</v>
       </c>
       <c r="EL78" t="n">
-        <v>0.6376194284157732</v>
+        <v>0.6376194284157731</v>
       </c>
       <c r="EM78" t="n">
         <v>0</v>
@@ -38170,16 +38170,16 @@
         <v>4.731875536836562</v>
       </c>
       <c r="W79" t="n">
-        <v>1038.585821605691</v>
+        <v>1038.58582160569</v>
       </c>
       <c r="X79" t="n">
-        <v>865.4881846714088</v>
+        <v>865.4881846714087</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>865.4881846714088</v>
+        <v>865.4881846714087</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -38347,13 +38347,13 @@
         <v>1041.086685448203</v>
       </c>
       <c r="CL79" t="n">
-        <v>867.5722378735022</v>
+        <v>867.5722378735023</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>867.5722378735022</v>
+        <v>867.5722378735023</v>
       </c>
       <c r="CP79" t="n">
         <v>0</v>
@@ -39144,28 +39144,28 @@
         <v>3.38698718383761</v>
       </c>
       <c r="W81" t="n">
-        <v>5242.753795319306</v>
+        <v>5242.753795319305</v>
       </c>
       <c r="X81" t="n">
-        <v>1092.24643169844</v>
+        <v>1092.246431698439</v>
       </c>
       <c r="Z81" t="n">
-        <v>535.2096094634715</v>
+        <v>535.2096094634713</v>
       </c>
       <c r="AA81" t="n">
-        <v>1092.24643169844</v>
+        <v>1092.246431698439</v>
       </c>
       <c r="AB81" t="n">
         <v>0.4900081098284956</v>
       </c>
       <c r="AD81" t="n">
-        <v>491.5108942642979</v>
+        <v>491.5108942642978</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>27.39893954415532</v>
+        <v>27.39893954415531</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -39183,7 +39183,7 @@
         <v>0</v>
       </c>
       <c r="AM81" t="n">
-        <v>508.2124210718736</v>
+        <v>508.2124210718735</v>
       </c>
       <c r="AN81" t="n">
         <v>0</v>
@@ -39318,7 +39318,7 @@
         <v>2.371703773805795</v>
       </c>
       <c r="CK81" t="n">
-        <v>3565.653179250505</v>
+        <v>3565.653179250506</v>
       </c>
       <c r="CL81" t="n">
         <v>0</v>
@@ -39631,16 +39631,16 @@
         <v>3.080163393495412</v>
       </c>
       <c r="W82" t="n">
-        <v>5572.372532618614</v>
+        <v>5572.372532618613</v>
       </c>
       <c r="X82" t="n">
-        <v>4643.643777182179</v>
+        <v>4643.643777182178</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4643.643777182179</v>
+        <v>4643.643777182178</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -39805,16 +39805,16 @@
         <v>3.16846440141259</v>
       </c>
       <c r="CK82" t="n">
-        <v>6151.190494387763</v>
+        <v>6151.190494387764</v>
       </c>
       <c r="CL82" t="n">
-        <v>5125.99207865647</v>
+        <v>5125.992078656471</v>
       </c>
       <c r="CN82" t="n">
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>5125.99207865647</v>
+        <v>5125.992078656471</v>
       </c>
       <c r="CP82" t="n">
         <v>0</v>
@@ -40605,7 +40605,7 @@
         <v>3.159629396518269</v>
       </c>
       <c r="W84" t="n">
-        <v>2037.631391399686</v>
+        <v>2037.631391399685</v>
       </c>
       <c r="X84" t="n">
         <v>1728.521127770336</v>
@@ -40617,7 +40617,7 @@
         <v>1728.521127770336</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.5066501866616031</v>
+        <v>0.5066501866616032</v>
       </c>
       <c r="AD84" t="n">
         <v>846.9753526074644</v>
@@ -40656,7 +40656,7 @@
         <v>0</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.5066501866616031</v>
+        <v>0.5066501866616032</v>
       </c>
       <c r="AR84" t="n">
         <v>0</v>
@@ -40770,7 +40770,7 @@
         <v>2015.833706970856</v>
       </c>
       <c r="CH84" t="n">
-        <v>0.02499189948061918</v>
+        <v>0.02499189948061919</v>
       </c>
       <c r="CI84" t="n">
         <v>0</v>
@@ -40791,10 +40791,10 @@
         <v>1891.481905077456</v>
       </c>
       <c r="CP84" t="n">
-        <v>0.5391833214354558</v>
+        <v>0.5391833214354557</v>
       </c>
       <c r="CR84" t="n">
-        <v>926.8261334879534</v>
+        <v>926.8261334879535</v>
       </c>
       <c r="CS84" t="n">
         <v>0</v>
@@ -40830,7 +40830,7 @@
         <v>0</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.5391833214354558</v>
+        <v>0.5391833214354557</v>
       </c>
       <c r="DF84" t="n">
         <v>0</v>
@@ -40857,7 +40857,7 @@
         <v>2136.350096137353</v>
       </c>
       <c r="DO84" t="n">
-        <v>0.02563177773439944</v>
+        <v>0.02563177773439945</v>
       </c>
       <c r="DP84" t="n">
         <v>0</v>
@@ -40878,7 +40878,7 @@
         <v>1967.56483631861</v>
       </c>
       <c r="DW84" t="n">
-        <v>0.5538958358461351</v>
+        <v>0.553895835846135</v>
       </c>
       <c r="DY84" t="n">
         <v>964.1067697961187</v>
@@ -40917,7 +40917,7 @@
         <v>0</v>
       </c>
       <c r="EL84" t="n">
-        <v>0.5538958358461351</v>
+        <v>0.553895835846135</v>
       </c>
       <c r="EM84" t="n">
         <v>0</v>
@@ -41092,7 +41092,7 @@
         <v>11.50945958474944</v>
       </c>
       <c r="W85" t="n">
-        <v>23504.35431224586</v>
+        <v>23504.35431224585</v>
       </c>
       <c r="X85" t="n">
         <v>19586.96192687155</v>
@@ -41266,7 +41266,7 @@
         <v>14.63673122459776</v>
       </c>
       <c r="CK85" t="n">
-        <v>29031.5507384767</v>
+        <v>29031.55073847671</v>
       </c>
       <c r="CL85" t="n">
         <v>24192.95894873059</v>
@@ -41579,16 +41579,16 @@
         <v>3.836486528249814</v>
       </c>
       <c r="W86" t="n">
-        <v>8461.567552408509</v>
+        <v>8461.567552408507</v>
       </c>
       <c r="X86" t="n">
-        <v>7051.306293673758</v>
+        <v>7051.306293673757</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>7051.306293673758</v>
+        <v>7051.306293673757</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -41753,7 +41753,7 @@
         <v>4.878910408199253</v>
       </c>
       <c r="CK86" t="n">
-        <v>10451.35826585161</v>
+        <v>10451.35826585162</v>
       </c>
       <c r="CL86" t="n">
         <v>8709.465221543012</v>
@@ -42066,7 +42066,7 @@
         <v>7.672973056499627</v>
       </c>
       <c r="W87" t="n">
-        <v>5641.045034939008</v>
+        <v>5641.045034939007</v>
       </c>
       <c r="X87" t="n">
         <v>4700.870862449173</v>
@@ -42240,7 +42240,7 @@
         <v>9.757820816398507</v>
       </c>
       <c r="CK87" t="n">
-        <v>6967.572177234408</v>
+        <v>6967.572177234409</v>
       </c>
       <c r="CL87" t="n">
         <v>5806.310147695342</v>
@@ -42556,19 +42556,19 @@
         <v>7812.109348630634</v>
       </c>
       <c r="X88" t="n">
-        <v>6625.828697950158</v>
+        <v>6625.828697950157</v>
       </c>
       <c r="Z88" t="n">
-        <v>4179.094247813461</v>
+        <v>4179.09424781346</v>
       </c>
       <c r="AA88" t="n">
-        <v>6625.828697950158</v>
+        <v>6625.828697950157</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.6307277833950572</v>
+        <v>0.6307277833950571</v>
       </c>
       <c r="AD88" t="n">
-        <v>4041.755505749597</v>
+        <v>4041.755505749596</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -42592,7 +42592,7 @@
         <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>4179.094247813461</v>
+        <v>4179.09424781346</v>
       </c>
       <c r="AN88" t="n">
         <v>0</v>
@@ -42604,7 +42604,7 @@
         <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.6307277833950572</v>
+        <v>0.6307277833950571</v>
       </c>
       <c r="AR88" t="n">
         <v>0</v>
@@ -42631,7 +42631,7 @@
         <v>7398.36093320792</v>
       </c>
       <c r="BA88" t="n">
-        <v>0.0162836902234389</v>
+        <v>0.01628369022343891</v>
       </c>
       <c r="BB88" t="n">
         <v>0</v>
@@ -42718,7 +42718,7 @@
         <v>8002.454778121067</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.01710847682020767</v>
+        <v>0.01710847682020768</v>
       </c>
       <c r="CI88" t="n">
         <v>0</v>
@@ -42730,19 +42730,19 @@
         <v>8888.206101288521</v>
       </c>
       <c r="CL88" t="n">
-        <v>7538.518526950233</v>
+        <v>7538.518526950234</v>
       </c>
       <c r="CN88" t="n">
         <v>5060.066345752826</v>
       </c>
       <c r="CO88" t="n">
-        <v>7538.518526950233</v>
+        <v>7538.518526950234</v>
       </c>
       <c r="CP88" t="n">
-        <v>0.6712282164808735</v>
+        <v>0.6712282164808734</v>
       </c>
       <c r="CR88" t="n">
-        <v>4598.496301439642</v>
+        <v>4598.496301439643</v>
       </c>
       <c r="CS88" t="n">
         <v>0</v>
@@ -42778,7 +42778,7 @@
         <v>0</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.6712282164808735</v>
+        <v>0.6712282164808734</v>
       </c>
       <c r="DF88" t="n">
         <v>0</v>
@@ -42820,13 +42820,13 @@
         <v>7993.60173224982</v>
       </c>
       <c r="DU88" t="n">
-        <v>5511.938479331496</v>
+        <v>5511.938479331495</v>
       </c>
       <c r="DV88" t="n">
         <v>7993.60173224982</v>
       </c>
       <c r="DW88" t="n">
-        <v>0.6895437956451886</v>
+        <v>0.6895437956451885</v>
       </c>
       <c r="DY88" t="n">
         <v>4876.09705667239</v>
@@ -42853,7 +42853,7 @@
         <v>0</v>
       </c>
       <c r="EH88" t="n">
-        <v>5511.938479331496</v>
+        <v>5511.938479331495</v>
       </c>
       <c r="EI88" t="n">
         <v>0</v>
@@ -42865,7 +42865,7 @@
         <v>0</v>
       </c>
       <c r="EL88" t="n">
-        <v>0.6895437956451886</v>
+        <v>0.6895437956451885</v>
       </c>
       <c r="EM88" t="n">
         <v>0</v>
@@ -43040,13 +43040,13 @@
         <v>3.183105887779057</v>
       </c>
       <c r="W89" t="n">
-        <v>6158.313838548567</v>
+        <v>6158.313838548566</v>
       </c>
       <c r="X89" t="n">
         <v>5224.092849325189</v>
       </c>
       <c r="Z89" t="n">
-        <v>2646.787617248154</v>
+        <v>2646.787617248153</v>
       </c>
       <c r="AA89" t="n">
         <v>5224.092849325189</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="AM89" t="n">
-        <v>2646.787617248154</v>
+        <v>2646.787617248153</v>
       </c>
       <c r="AN89" t="n">
         <v>0</v>
@@ -43217,19 +43217,19 @@
         <v>6739.452214597944</v>
       </c>
       <c r="CL89" t="n">
-        <v>5717.072082664087</v>
+        <v>5717.072082664088</v>
       </c>
       <c r="CN89" t="n">
         <v>3082.549914416741</v>
       </c>
       <c r="CO89" t="n">
-        <v>5717.072082664087</v>
+        <v>5717.072082664088</v>
       </c>
       <c r="CP89" t="n">
-        <v>0.5391833214354557</v>
+        <v>0.5391833214354556</v>
       </c>
       <c r="CR89" t="n">
-        <v>2801.365320505402</v>
+        <v>2801.365320505403</v>
       </c>
       <c r="CS89" t="n">
         <v>0</v>
@@ -43265,7 +43265,7 @@
         <v>0</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.5391833214354557</v>
+        <v>0.5391833214354556</v>
       </c>
       <c r="DF89" t="n">
         <v>0</v>
@@ -43307,7 +43307,7 @@
         <v>5947.011910281363</v>
       </c>
       <c r="DU89" t="n">
-        <v>3294.025132832217</v>
+        <v>3294.025132832216</v>
       </c>
       <c r="DV89" t="n">
         <v>5947.011910281363</v>
@@ -43340,7 +43340,7 @@
         <v>0</v>
       </c>
       <c r="EH89" t="n">
-        <v>3294.025132832217</v>
+        <v>3294.025132832216</v>
       </c>
       <c r="EI89" t="n">
         <v>0</v>
@@ -43710,7 +43710,7 @@
         <v>0</v>
       </c>
       <c r="CO90" t="n">
-        <v>15.45193951658787</v>
+        <v>15.45193951658788</v>
       </c>
       <c r="CP90" t="n">
         <v>0</v>
@@ -44023,7 +44023,7 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>38.42443111934795</v>
+        <v>38.42443111934794</v>
       </c>
       <c r="AB91" t="n">
         <v>0</v>
@@ -44997,7 +44997,7 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>238.4821280269546</v>
+        <v>238.4821280269545</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -45658,7 +45658,7 @@
         <v>2941.902268745102</v>
       </c>
       <c r="CO94" t="n">
-        <v>7576.216593822147</v>
+        <v>7576.216593822148</v>
       </c>
       <c r="CP94" t="n">
         <v>0.3883075717692666</v>
@@ -45742,13 +45742,13 @@
         <v>0</v>
       </c>
       <c r="DU94" t="n">
-        <v>4445.278618004751</v>
+        <v>4445.27861800475</v>
       </c>
       <c r="DV94" t="n">
         <v>11082.83952455333</v>
       </c>
       <c r="DW94" t="n">
-        <v>0.401095640531158</v>
+        <v>0.4010956405311579</v>
       </c>
       <c r="DY94" t="n">
         <v>3878.993833593664</v>
@@ -45787,7 +45787,7 @@
         <v>60.46528800400252</v>
       </c>
       <c r="EL94" t="n">
-        <v>0.3956398827472394</v>
+        <v>0.3956398827472393</v>
       </c>
       <c r="EM94" t="n">
         <v>0</v>
@@ -45796,7 +45796,7 @@
         <v>0</v>
       </c>
       <c r="EO94" t="n">
-        <v>0.005455757783918599</v>
+        <v>0.0054557577839186</v>
       </c>
       <c r="EQ94" t="n">
         <v>677.5021914512882</v>
@@ -46145,7 +46145,7 @@
         <v>2941.902268745102</v>
       </c>
       <c r="CO95" t="n">
-        <v>7576.216593822147</v>
+        <v>7576.216593822148</v>
       </c>
       <c r="CP95" t="n">
         <v>0.3883075717692666</v>
@@ -46229,13 +46229,13 @@
         <v>0</v>
       </c>
       <c r="DU95" t="n">
-        <v>4445.278618004751</v>
+        <v>4445.27861800475</v>
       </c>
       <c r="DV95" t="n">
         <v>11082.83952455333</v>
       </c>
       <c r="DW95" t="n">
-        <v>0.401095640531158</v>
+        <v>0.4010956405311579</v>
       </c>
       <c r="DY95" t="n">
         <v>3878.993833593664</v>
@@ -46274,7 +46274,7 @@
         <v>60.46528800400252</v>
       </c>
       <c r="EL95" t="n">
-        <v>0.3956398827472394</v>
+        <v>0.3956398827472393</v>
       </c>
       <c r="EM95" t="n">
         <v>0</v>
@@ -46283,7 +46283,7 @@
         <v>0</v>
       </c>
       <c r="EO95" t="n">
-        <v>0.005455757783918599</v>
+        <v>0.0054557577839186</v>
       </c>
       <c r="EQ95" t="n">
         <v>677.5021914512882</v>
@@ -46458,7 +46458,7 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>6806.012738359744</v>
+        <v>6806.012738359743</v>
       </c>
       <c r="AB96" t="n">
         <v>0</v>
@@ -46632,7 +46632,7 @@
         <v>0</v>
       </c>
       <c r="CO96" t="n">
-        <v>7274.059134203682</v>
+        <v>7274.059134203683</v>
       </c>
       <c r="CP96" t="n">
         <v>0</v>
@@ -46945,7 +46945,7 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>330.8259584972395</v>
+        <v>330.8259584972394</v>
       </c>
       <c r="AB97" t="n">
         <v>0</v>
@@ -47119,7 +47119,7 @@
         <v>0</v>
       </c>
       <c r="CO97" t="n">
-        <v>353.5767089702054</v>
+        <v>353.5767089702055</v>
       </c>
       <c r="CP97" t="n">
         <v>0</v>
@@ -47423,16 +47423,16 @@
         <v>7.30389596184621</v>
       </c>
       <c r="W98" t="n">
-        <v>7070.877285949316</v>
+        <v>7070.877285949315</v>
       </c>
       <c r="X98" t="n">
-        <v>5892.397738291096</v>
+        <v>5892.397738291095</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>5892.397738291096</v>
+        <v>5892.397738291095</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
@@ -47913,19 +47913,19 @@
         <v>3240.222505525358</v>
       </c>
       <c r="X99" t="n">
-        <v>2792.254099211645</v>
+        <v>2792.254099211644</v>
       </c>
       <c r="Z99" t="n">
-        <v>1774.12640433764</v>
+        <v>1774.126404337639</v>
       </c>
       <c r="AA99" t="n">
-        <v>2792.254099211645</v>
+        <v>2792.254099211644</v>
       </c>
       <c r="AB99" t="n">
         <v>0.6353742679932103</v>
       </c>
       <c r="AD99" t="n">
-        <v>1675.352459526987</v>
+        <v>1675.352459526986</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -47934,7 +47934,7 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>42.46822622025884</v>
+        <v>42.46822622025883</v>
       </c>
       <c r="AH99" t="n">
         <v>0.6</v>
@@ -47958,7 +47958,7 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>41.84551384106022</v>
+        <v>41.84551384106021</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.6203879836672692</v>
@@ -47988,7 +47988,7 @@
         <v>3023.374890491798</v>
       </c>
       <c r="BA99" t="n">
-        <v>0.005566019303071898</v>
+        <v>0.005566019303071899</v>
       </c>
       <c r="BB99" t="n">
         <v>0</v>
@@ -48075,7 +48075,7 @@
         <v>1284.381270228583</v>
       </c>
       <c r="CH99" t="n">
-        <v>0.002238673642108072</v>
+        <v>0.002238673642108073</v>
       </c>
       <c r="CI99" t="n">
         <v>0</v>
@@ -48090,13 +48090,13 @@
         <v>1212.467272740614</v>
       </c>
       <c r="CN99" t="n">
-        <v>513.2584864381809</v>
+        <v>513.2584864381807</v>
       </c>
       <c r="CO99" t="n">
         <v>1212.467272740614</v>
       </c>
       <c r="CP99" t="n">
-        <v>0.4233173941907985</v>
+        <v>0.4233173941907984</v>
       </c>
       <c r="CR99" t="n">
         <v>447.9742786922914</v>
@@ -48123,7 +48123,7 @@
         <v>0.01880771278686523</v>
       </c>
       <c r="DA99" t="n">
-        <v>492.939305108086</v>
+        <v>492.9393051080859</v>
       </c>
       <c r="DB99" t="n">
         <v>0</v>
@@ -48135,7 +48135,7 @@
         <v>20.31918133009478</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.4065588541568345</v>
+        <v>0.4065588541568343</v>
       </c>
       <c r="DF99" t="n">
         <v>0</v>
@@ -48144,7 +48144,7 @@
         <v>0</v>
       </c>
       <c r="DH99" t="n">
-        <v>0.01675854003396404</v>
+        <v>0.01675854003396405</v>
       </c>
       <c r="DJ99" t="n">
         <v>1.694567293719186</v>
@@ -48397,22 +48397,22 @@
         <v>0.9858663919007954</v>
       </c>
       <c r="W100" t="n">
-        <v>648.9366621515936</v>
+        <v>648.9366621515935</v>
       </c>
       <c r="X100" t="n">
-        <v>559.2155386947786</v>
+        <v>559.2155386947785</v>
       </c>
       <c r="Z100" t="n">
-        <v>355.309275996983</v>
+        <v>355.3092759969829</v>
       </c>
       <c r="AA100" t="n">
-        <v>559.2155386947786</v>
+        <v>559.2155386947785</v>
       </c>
       <c r="AB100" t="n">
         <v>0.6353708926370013</v>
       </c>
       <c r="AD100" t="n">
-        <v>335.5293232168672</v>
+        <v>335.5293232168671</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -48421,7 +48421,7 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>8.503360440669242</v>
+        <v>8.50336044066924</v>
       </c>
       <c r="AH100" t="n">
         <v>0.6</v>
@@ -48436,7 +48436,7 @@
         <v>0.01520587296360948</v>
       </c>
       <c r="AM100" t="n">
-        <v>346.9306004862596</v>
+        <v>346.9306004862594</v>
       </c>
       <c r="AN100" t="n">
         <v>0</v>
@@ -48445,7 +48445,7 @@
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>8.378675510723507</v>
+        <v>8.378675510723506</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.6203879836672693</v>
@@ -48583,10 +48583,10 @@
         <v>242.8249285035001</v>
       </c>
       <c r="CP100" t="n">
-        <v>0.4233119594622176</v>
+        <v>0.4233119594622175</v>
       </c>
       <c r="CR100" t="n">
-        <v>89.71732651305476</v>
+        <v>89.71732651305477</v>
       </c>
       <c r="CS100" t="n">
         <v>0</v>
@@ -48595,7 +48595,7 @@
         <v>0</v>
       </c>
       <c r="CU100" t="n">
-        <v>4.565500458653376</v>
+        <v>4.565500458653377</v>
       </c>
       <c r="CV100" t="n">
         <v>0.3694732952912681</v>
@@ -48619,10 +48619,10 @@
         <v>0</v>
       </c>
       <c r="DD100" t="n">
-        <v>4.068071597991277</v>
+        <v>4.068071597991278</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.4065588541568344</v>
+        <v>0.4065588541568343</v>
       </c>
       <c r="DF100" t="n">
         <v>0</v>
@@ -48899,7 +48899,7 @@
         <v>0.5997083842116936</v>
       </c>
       <c r="AD101" t="n">
-        <v>1886.314230304942</v>
+        <v>1886.314230304941</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -49070,7 +49070,7 @@
         <v>3109.498029264309</v>
       </c>
       <c r="CP101" t="n">
-        <v>0.638216992719519</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="CR101" t="n">
         <v>1803.508856973299</v>
@@ -49109,7 +49109,7 @@
         <v>0</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.638216992719519</v>
+        <v>0.6382169927195188</v>
       </c>
       <c r="DF101" t="n">
         <v>0</v>
@@ -49151,13 +49151,13 @@
         <v>1242.985789676743</v>
       </c>
       <c r="DU101" t="n">
-        <v>501.831572153732</v>
+        <v>501.8315721537319</v>
       </c>
       <c r="DV101" t="n">
         <v>1242.985789676743</v>
       </c>
       <c r="DW101" t="n">
-        <v>0.4037307395800888</v>
+        <v>0.4037307395800886</v>
       </c>
       <c r="DY101" t="n">
         <v>443.9417205216825</v>
@@ -49184,7 +49184,7 @@
         <v>0</v>
       </c>
       <c r="EH101" t="n">
-        <v>501.831572153732</v>
+        <v>501.8315721537319</v>
       </c>
       <c r="EI101" t="n">
         <v>0</v>
@@ -49196,7 +49196,7 @@
         <v>0</v>
       </c>
       <c r="EL101" t="n">
-        <v>0.4037307395800888</v>
+        <v>0.4037307395800886</v>
       </c>
       <c r="EM101" t="n">
         <v>0</v>
@@ -50041,7 +50041,7 @@
         <v>0</v>
       </c>
       <c r="CO103" t="n">
-        <v>639.1450573877005</v>
+        <v>639.1450573877006</v>
       </c>
       <c r="CP103" t="n">
         <v>0</v>
@@ -50345,7 +50345,7 @@
         <v>1.216256599457665</v>
       </c>
       <c r="W104" t="n">
-        <v>38.42435449306641</v>
+        <v>38.4243544930664</v>
       </c>
       <c r="X104" t="n">
         <v>32.02029541088868</v>
@@ -50519,7 +50519,7 @@
         <v>1.409583136540869</v>
       </c>
       <c r="CK104" t="n">
-        <v>47.68517796875948</v>
+        <v>47.68517796875949</v>
       </c>
       <c r="CL104" t="n">
         <v>39.73764830729957</v>
@@ -50835,13 +50835,13 @@
         <v>4715.341825212276</v>
       </c>
       <c r="X105" t="n">
-        <v>3929.451521010231</v>
+        <v>3929.45152101023</v>
       </c>
       <c r="Z105" t="n">
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>3929.451521010231</v>
+        <v>3929.45152101023</v>
       </c>
       <c r="AB105" t="n">
         <v>0</v>
@@ -51009,13 +51009,13 @@
         <v>4967.449363823625</v>
       </c>
       <c r="CL105" t="n">
-        <v>4139.541136519688</v>
+        <v>4139.541136519689</v>
       </c>
       <c r="CN105" t="n">
         <v>0</v>
       </c>
       <c r="CO105" t="n">
-        <v>4139.541136519688</v>
+        <v>4139.541136519689</v>
       </c>
       <c r="CP105" t="n">
         <v>0</v>
@@ -51415,7 +51415,7 @@
         <v>0</v>
       </c>
       <c r="BH106" t="n">
-        <v>1711.826156796962</v>
+        <v>1711.826156796961</v>
       </c>
       <c r="BI106" t="n">
         <v>0</v>
@@ -51589,7 +51589,7 @@
         <v>0</v>
       </c>
       <c r="DV106" t="n">
-        <v>77.86836708085941</v>
+        <v>77.8683670808594</v>
       </c>
       <c r="DW106" t="n">
         <v>0</v>
@@ -51676,7 +51676,7 @@
         <v>0</v>
       </c>
       <c r="FC106" t="n">
-        <v>26.77866580024589</v>
+        <v>26.77866580024588</v>
       </c>
       <c r="FD106" t="n">
         <v>0</v>
@@ -51980,7 +51980,7 @@
         <v>5.838838268947272</v>
       </c>
       <c r="CK107" t="n">
-        <v>1314.02397203951</v>
+        <v>1314.023972039511</v>
       </c>
       <c r="CL107" t="n">
         <v>1095.019976699592</v>
@@ -52293,7 +52293,7 @@
         <v>0.8369914951330503</v>
       </c>
       <c r="W108" t="n">
-        <v>845.2901470689019</v>
+        <v>845.2901470689018</v>
       </c>
       <c r="X108" t="n">
         <v>704.4084558907515</v>
@@ -52467,16 +52467,16 @@
         <v>0.04261690550526381</v>
       </c>
       <c r="CK108" t="n">
-        <v>43.97203993928418</v>
+        <v>43.97203993928419</v>
       </c>
       <c r="CL108" t="n">
-        <v>36.64336661607015</v>
+        <v>36.64336661607016</v>
       </c>
       <c r="CN108" t="n">
         <v>0</v>
       </c>
       <c r="CO108" t="n">
-        <v>36.64336661607015</v>
+        <v>36.64336661607016</v>
       </c>
       <c r="CP108" t="n">
         <v>0</v>
@@ -52780,16 +52780,16 @@
         <v>5.021948970798301</v>
       </c>
       <c r="W109" t="n">
-        <v>9660.458823644594</v>
+        <v>9660.458823644592</v>
       </c>
       <c r="X109" t="n">
-        <v>8050.382353037163</v>
+        <v>8050.382353037162</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>8050.382353037163</v>
+        <v>8050.382353037162</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -52954,16 +52954,16 @@
         <v>0.2557014330315829</v>
       </c>
       <c r="CK109" t="n">
-        <v>502.5375993061049</v>
+        <v>502.537599306105</v>
       </c>
       <c r="CL109" t="n">
-        <v>418.7813327550874</v>
+        <v>418.7813327550875</v>
       </c>
       <c r="CN109" t="n">
         <v>0</v>
       </c>
       <c r="CO109" t="n">
-        <v>418.7813327550874</v>
+        <v>418.7813327550875</v>
       </c>
       <c r="CP109" t="n">
         <v>0</v>
@@ -53441,7 +53441,7 @@
         <v>0.04261690550526381</v>
       </c>
       <c r="CK110" t="n">
-        <v>94.22623314031551</v>
+        <v>94.22623314031553</v>
       </c>
       <c r="CL110" t="n">
         <v>78.52186095026292</v>
@@ -53757,13 +53757,13 @@
         <v>15094.46691194468</v>
       </c>
       <c r="X111" t="n">
-        <v>12578.72242662057</v>
+        <v>12578.72242662056</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>12578.72242662057</v>
+        <v>12578.72242662056</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -53928,16 +53928,16 @@
         <v>0.3835521495473743</v>
       </c>
       <c r="CK111" t="n">
-        <v>785.214998915789</v>
+        <v>785.2149989157891</v>
       </c>
       <c r="CL111" t="n">
-        <v>654.3458324298241</v>
+        <v>654.3458324298242</v>
       </c>
       <c r="CN111" t="n">
         <v>0</v>
       </c>
       <c r="CO111" t="n">
-        <v>654.3458324298241</v>
+        <v>654.3458324298242</v>
       </c>
       <c r="CP111" t="n">
         <v>0</v>
@@ -54337,7 +54337,7 @@
         <v>0</v>
       </c>
       <c r="BH112" t="n">
-        <v>129221.8613642014</v>
+        <v>129221.8613642013</v>
       </c>
       <c r="BI112" t="n">
         <v>0</v>
@@ -54424,7 +54424,7 @@
         <v>0</v>
       </c>
       <c r="CO112" t="n">
-        <v>88864.69802880238</v>
+        <v>88864.69802880235</v>
       </c>
       <c r="CP112" t="n">
         <v>0</v>
@@ -54511,7 +54511,7 @@
         <v>0</v>
       </c>
       <c r="DV112" t="n">
-        <v>64630.67175250717</v>
+        <v>64630.67175250716</v>
       </c>
       <c r="DW112" t="n">
         <v>0</v>
@@ -54598,7 +54598,7 @@
         <v>0</v>
       </c>
       <c r="FC112" t="n">
-        <v>65106.69296448425</v>
+        <v>65106.69296448424</v>
       </c>
       <c r="FD112" t="n">
         <v>0</v>
@@ -54911,7 +54911,7 @@
         <v>0</v>
       </c>
       <c r="CO113" t="n">
-        <v>7405.391502400196</v>
+        <v>7405.391502400194</v>
       </c>
       <c r="CP113" t="n">
         <v>0</v>
@@ -54998,7 +54998,7 @@
         <v>0</v>
       </c>
       <c r="DV113" t="n">
-        <v>5385.889312708932</v>
+        <v>5385.88931270893</v>
       </c>
       <c r="DW113" t="n">
         <v>0</v>
@@ -55085,7 +55085,7 @@
         <v>0</v>
       </c>
       <c r="FC113" t="n">
-        <v>5425.557747040353</v>
+        <v>5425.557747040351</v>
       </c>
       <c r="FD113" t="n">
         <v>0</v>
@@ -55218,13 +55218,13 @@
         <v>598.9184978640762</v>
       </c>
       <c r="X114" t="n">
-        <v>499.0987482200636</v>
+        <v>499.0987482200635</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>499.0987482200636</v>
+        <v>499.0987482200635</v>
       </c>
       <c r="AB114" t="n">
         <v>0</v>
@@ -55389,7 +55389,7 @@
         <v>0.9947800511531335</v>
       </c>
       <c r="CK114" t="n">
-        <v>637.8464947201321</v>
+        <v>637.8464947201322</v>
       </c>
       <c r="CL114" t="n">
         <v>531.5387456001101</v>
@@ -55711,7 +55711,7 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>18.43159244914891</v>
+        <v>18.4315924491489</v>
       </c>
       <c r="AB115" t="n">
         <v>0</v>
@@ -55885,7 +55885,7 @@
         <v>0</v>
       </c>
       <c r="CO115" t="n">
-        <v>21.87544225803446</v>
+        <v>21.87544225803447</v>
       </c>
       <c r="CP115" t="n">
         <v>0</v>
@@ -56198,7 +56198,7 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>60.9247751046291</v>
+        <v>60.92477510462909</v>
       </c>
       <c r="AB116" t="n">
         <v>0</v>
@@ -56372,7 +56372,7 @@
         <v>0</v>
       </c>
       <c r="CO116" t="n">
-        <v>74.29319628704809</v>
+        <v>74.2931962870481</v>
       </c>
       <c r="CP116" t="n">
         <v>0</v>
@@ -56772,7 +56772,7 @@
         <v>0</v>
       </c>
       <c r="BH117" t="n">
-        <v>1218.487402887545</v>
+        <v>1218.487402887544</v>
       </c>
       <c r="BI117" t="n">
         <v>0</v>
@@ -57250,22 +57250,22 @@
         <v>3.340712257225895</v>
       </c>
       <c r="BD118" t="n">
-        <v>4316.649210291087</v>
+        <v>4316.649210291086</v>
       </c>
       <c r="BE118" t="n">
-        <v>2369.47591126708</v>
+        <v>2369.475911267079</v>
       </c>
       <c r="BG118" t="n">
-        <v>420.8281148153462</v>
+        <v>420.8281148153461</v>
       </c>
       <c r="BH118" t="n">
-        <v>2369.47591126708</v>
+        <v>2369.475911267079</v>
       </c>
       <c r="BI118" t="n">
-        <v>0.1776038797500616</v>
+        <v>0.1776038797500617</v>
       </c>
       <c r="BK118" t="n">
-        <v>355.421386690062</v>
+        <v>355.4213866900619</v>
       </c>
       <c r="BL118" t="n">
         <v>0</v>
@@ -57274,7 +57274,7 @@
         <v>0</v>
       </c>
       <c r="BN118" t="n">
-        <v>36.57212548996726</v>
+        <v>36.57212548996724</v>
       </c>
       <c r="BO118" t="n">
         <v>0.15</v>
@@ -57289,7 +57289,7 @@
         <v>0.01543468972023027</v>
       </c>
       <c r="BT118" t="n">
-        <v>384.7892647196475</v>
+        <v>384.7892647196473</v>
       </c>
       <c r="BU118" t="n">
         <v>0</v>
@@ -57298,10 +57298,10 @@
         <v>0</v>
       </c>
       <c r="BW118" t="n">
-        <v>36.03885009569876</v>
+        <v>36.03885009569875</v>
       </c>
       <c r="BX118" t="n">
-        <v>0.162394250513347</v>
+        <v>0.1623942505133471</v>
       </c>
       <c r="BY118" t="n">
         <v>0</v>
@@ -57337,13 +57337,13 @@
         <v>3.442236502722989</v>
       </c>
       <c r="CK118" t="n">
-        <v>4662.672795207819</v>
+        <v>4662.672795207817</v>
       </c>
       <c r="CL118" t="n">
         <v>2559.413640567809</v>
       </c>
       <c r="CN118" t="n">
-        <v>471.6978734784187</v>
+        <v>471.6978734784186</v>
       </c>
       <c r="CO118" t="n">
         <v>2559.413640567809</v>
@@ -57352,7 +57352,7 @@
         <v>0.184299194941296</v>
       </c>
       <c r="CR118" t="n">
-        <v>383.9120460851713</v>
+        <v>383.9120460851712</v>
       </c>
       <c r="CS118" t="n">
         <v>0</v>
@@ -57361,7 +57361,7 @@
         <v>0</v>
       </c>
       <c r="CU118" t="n">
-        <v>39.5037554078889</v>
+        <v>39.50375540788889</v>
       </c>
       <c r="CV118" t="n">
         <v>0.15</v>
@@ -57376,7 +57376,7 @@
         <v>0.01543468972023019</v>
       </c>
       <c r="DA118" t="n">
-        <v>433.087060529274</v>
+        <v>433.0870605292739</v>
       </c>
       <c r="DB118" t="n">
         <v>0</v>
@@ -57385,7 +57385,7 @@
         <v>0</v>
       </c>
       <c r="DD118" t="n">
-        <v>38.6108129491447</v>
+        <v>38.61081294914469</v>
       </c>
       <c r="DE118" t="n">
         <v>0.1692133907800824</v>
@@ -57427,19 +57427,19 @@
         <v>4985.751522459967</v>
       </c>
       <c r="DS118" t="n">
-        <v>2736.75658051339</v>
+        <v>2736.756580513389</v>
       </c>
       <c r="DU118" t="n">
-        <v>517.1859257695901</v>
+        <v>517.1859257695899</v>
       </c>
       <c r="DV118" t="n">
-        <v>2736.75658051339</v>
+        <v>2736.756580513389</v>
       </c>
       <c r="DW118" t="n">
         <v>0.1889776860142128</v>
       </c>
       <c r="DY118" t="n">
-        <v>410.5134870770085</v>
+        <v>410.5134870770083</v>
       </c>
       <c r="DZ118" t="n">
         <v>0</v>
@@ -57448,7 +57448,7 @@
         <v>0</v>
       </c>
       <c r="EB118" t="n">
-        <v>42.24098866002186</v>
+        <v>42.24098866002184</v>
       </c>
       <c r="EC118" t="n">
         <v>0.15</v>
@@ -57463,7 +57463,7 @@
         <v>0.01543468972023001</v>
       </c>
       <c r="EH118" t="n">
-        <v>476.1365507882433</v>
+        <v>476.1365507882431</v>
       </c>
       <c r="EI118" t="n">
         <v>0</v>
@@ -57472,7 +57472,7 @@
         <v>0</v>
       </c>
       <c r="EK118" t="n">
-        <v>41.04937498134681</v>
+        <v>41.04937498134679</v>
       </c>
       <c r="EL118" t="n">
         <v>0.1739784072059944</v>
@@ -57511,22 +57511,22 @@
         <v>3.583269332794696</v>
       </c>
       <c r="EY118" t="n">
-        <v>5334.755996006727</v>
+        <v>5334.755996006726</v>
       </c>
       <c r="EZ118" t="n">
-        <v>2928.330565960712</v>
+        <v>2928.330565960711</v>
       </c>
       <c r="FB118" t="n">
-        <v>566.2247503714775</v>
+        <v>566.2247503714773</v>
       </c>
       <c r="FC118" t="n">
-        <v>2928.330565960712</v>
+        <v>2928.330565960711</v>
       </c>
       <c r="FD118" t="n">
         <v>0.193360939831502</v>
       </c>
       <c r="FF118" t="n">
-        <v>439.2495848941068</v>
+        <v>439.2495848941067</v>
       </c>
       <c r="FG118" t="n">
         <v>0</v>
@@ -57535,7 +57535,7 @@
         <v>0</v>
       </c>
       <c r="FI118" t="n">
-        <v>45.19787368386941</v>
+        <v>45.1978736838694</v>
       </c>
       <c r="FJ118" t="n">
         <v>0.15</v>
@@ -57550,7 +57550,7 @@
         <v>0.0154346897202301</v>
       </c>
       <c r="FO118" t="n">
-        <v>522.5392893285915</v>
+        <v>522.5392893285914</v>
       </c>
       <c r="FP118" t="n">
         <v>0</v>
@@ -57559,7 +57559,7 @@
         <v>0</v>
       </c>
       <c r="FR118" t="n">
-        <v>43.68546104288595</v>
+        <v>43.68546104288593</v>
       </c>
       <c r="FS118" t="n">
         <v>0.1784427261739692</v>
@@ -57743,16 +57743,16 @@
         <v>0</v>
       </c>
       <c r="BG119" t="n">
-        <v>422.4814196545838</v>
+        <v>422.4814196545837</v>
       </c>
       <c r="BH119" t="n">
-        <v>2378.784856778655</v>
+        <v>2378.784856778654</v>
       </c>
       <c r="BI119" t="n">
-        <v>0.1776038797500616</v>
+        <v>0.1776038797500617</v>
       </c>
       <c r="BK119" t="n">
-        <v>356.8177285167982</v>
+        <v>356.8177285167981</v>
       </c>
       <c r="BL119" t="n">
         <v>0</v>
@@ -57761,7 +57761,7 @@
         <v>0</v>
       </c>
       <c r="BN119" t="n">
-        <v>36.71580617556094</v>
+        <v>36.71580617556093</v>
       </c>
       <c r="BO119" t="n">
         <v>0.15</v>
@@ -57776,7 +57776,7 @@
         <v>0.01543468972023027</v>
       </c>
       <c r="BT119" t="n">
-        <v>386.3009839490692</v>
+        <v>386.3009839490691</v>
       </c>
       <c r="BU119" t="n">
         <v>0</v>
@@ -57785,10 +57785,10 @@
         <v>0</v>
       </c>
       <c r="BW119" t="n">
-        <v>36.18043570551459</v>
+        <v>36.18043570551458</v>
       </c>
       <c r="BX119" t="n">
-        <v>0.162394250513347</v>
+        <v>0.1623942505133471</v>
       </c>
       <c r="BY119" t="n">
         <v>0</v>
@@ -57833,7 +57833,7 @@
         <v>475.0818190637262</v>
       </c>
       <c r="CO119" t="n">
-        <v>2577.774792858168</v>
+        <v>2577.774792858167</v>
       </c>
       <c r="CP119" t="n">
         <v>0.184299194941296</v>
@@ -57848,7 +57848,7 @@
         <v>0</v>
       </c>
       <c r="CU119" t="n">
-        <v>39.78715409639647</v>
+        <v>39.78715409639646</v>
       </c>
       <c r="CV119" t="n">
         <v>0.15</v>
@@ -57863,7 +57863,7 @@
         <v>0.01543468972023019</v>
       </c>
       <c r="DA119" t="n">
-        <v>436.194013366955</v>
+        <v>436.1940133669549</v>
       </c>
       <c r="DB119" t="n">
         <v>0</v>
@@ -57872,7 +57872,7 @@
         <v>0</v>
       </c>
       <c r="DD119" t="n">
-        <v>38.88780569677127</v>
+        <v>38.88780569677126</v>
       </c>
       <c r="DE119" t="n">
         <v>0.1692133907800824</v>
@@ -57926,7 +57926,7 @@
         <v>0.1889776860142128</v>
       </c>
       <c r="DY119" t="n">
-        <v>415.0023847627886</v>
+        <v>415.0023847627885</v>
       </c>
       <c r="DZ119" t="n">
         <v>0</v>
@@ -57950,7 +57950,7 @@
         <v>0.01543468972023001</v>
       </c>
       <c r="EH119" t="n">
-        <v>481.3430259181279</v>
+        <v>481.3430259181278</v>
       </c>
       <c r="EI119" t="n">
         <v>0</v>
@@ -58013,7 +58013,7 @@
         <v>0.193360939831502</v>
       </c>
       <c r="FF119" t="n">
-        <v>445.120615512637</v>
+        <v>445.1206155126369</v>
       </c>
       <c r="FG119" t="n">
         <v>0</v>
@@ -58022,7 +58022,7 @@
         <v>0</v>
       </c>
       <c r="FI119" t="n">
-        <v>45.80199059010263</v>
+        <v>45.80199059010262</v>
       </c>
       <c r="FJ119" t="n">
         <v>0.15</v>
@@ -58046,7 +58046,7 @@
         <v>0</v>
       </c>
       <c r="FR119" t="n">
-        <v>44.26936297060027</v>
+        <v>44.26936297060026</v>
       </c>
       <c r="FS119" t="n">
         <v>0.1784427261739692</v>
@@ -58140,13 +58140,13 @@
         <v>278.194158386187</v>
       </c>
       <c r="X120" t="n">
-        <v>225.9063479274651</v>
+        <v>225.906347927465</v>
       </c>
       <c r="Z120" t="n">
         <v>144.8212364779685</v>
       </c>
       <c r="AA120" t="n">
-        <v>225.9063479274651</v>
+        <v>225.906347927465</v>
       </c>
       <c r="AB120" t="n">
         <v>0.641067583122845</v>
@@ -58317,7 +58317,7 @@
         <v>108.17450415357</v>
       </c>
       <c r="CN120" t="n">
-        <v>45.4452792062478</v>
+        <v>45.44527920624779</v>
       </c>
       <c r="CO120" t="n">
         <v>108.17450415357</v>
@@ -58350,7 +58350,7 @@
         <v>0</v>
       </c>
       <c r="DA120" t="n">
-        <v>45.4452792062478</v>
+        <v>45.44527920624779</v>
       </c>
       <c r="DB120" t="n">
         <v>0</v>
@@ -59598,16 +59598,16 @@
         <v>4.064411080813915</v>
       </c>
       <c r="W123" t="n">
-        <v>8677.365070241494</v>
+        <v>8677.365070241493</v>
       </c>
       <c r="X123" t="n">
-        <v>7231.137558534579</v>
+        <v>7231.137558534578</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>7231.137558534579</v>
+        <v>7231.137558534578</v>
       </c>
       <c r="AB123" t="n">
         <v>0</v>
@@ -59772,16 +59772,16 @@
         <v>4.109917537573565</v>
       </c>
       <c r="CK123" t="n">
-        <v>9305.906323413403</v>
+        <v>9305.906323413405</v>
       </c>
       <c r="CL123" t="n">
-        <v>7754.921936177836</v>
+        <v>7754.921936177837</v>
       </c>
       <c r="CN123" t="n">
         <v>0</v>
       </c>
       <c r="CO123" t="n">
-        <v>7754.921936177836</v>
+        <v>7754.921936177837</v>
       </c>
       <c r="CP123" t="n">
         <v>0</v>
@@ -60085,7 +60085,7 @@
         <v>4.064411080813915</v>
       </c>
       <c r="W124" t="n">
-        <v>5784.910046827663</v>
+        <v>5784.910046827662</v>
       </c>
       <c r="X124" t="n">
         <v>4820.758372356386</v>
@@ -60262,13 +60262,13 @@
         <v>6203.937548942269</v>
       </c>
       <c r="CL124" t="n">
-        <v>5169.947957451891</v>
+        <v>5169.947957451892</v>
       </c>
       <c r="CN124" t="n">
         <v>0</v>
       </c>
       <c r="CO124" t="n">
-        <v>5169.947957451891</v>
+        <v>5169.947957451892</v>
       </c>
       <c r="CP124" t="n">
         <v>0</v>
@@ -61059,7 +61059,7 @@
         <v>3.264037424115284</v>
       </c>
       <c r="W126" t="n">
-        <v>3674.786733996727</v>
+        <v>3674.786733996726</v>
       </c>
       <c r="X126" t="n">
         <v>3062.322278330606</v>
@@ -61233,7 +61233,7 @@
         <v>3.524984088354316</v>
       </c>
       <c r="CK126" t="n">
-        <v>4249.575143752396</v>
+        <v>4249.575143752397</v>
       </c>
       <c r="CL126" t="n">
         <v>3541.312619793664</v>
@@ -62036,13 +62036,13 @@
         <v>115.65154956137</v>
       </c>
       <c r="X128" t="n">
-        <v>96.37629130114171</v>
+        <v>96.37629130114169</v>
       </c>
       <c r="Z128" t="n">
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>96.37629130114171</v>
+        <v>96.37629130114169</v>
       </c>
       <c r="AB128" t="n">
         <v>0</v>
@@ -62207,16 +62207,16 @@
         <v>0.9947800511531335</v>
       </c>
       <c r="CK128" t="n">
-        <v>118.9017842845543</v>
+        <v>118.9017842845544</v>
       </c>
       <c r="CL128" t="n">
-        <v>99.08482023712862</v>
+        <v>99.08482023712864</v>
       </c>
       <c r="CN128" t="n">
         <v>0</v>
       </c>
       <c r="CO128" t="n">
-        <v>99.08482023712862</v>
+        <v>99.08482023712864</v>
       </c>
       <c r="CP128" t="n">
         <v>0</v>
@@ -62523,13 +62523,13 @@
         <v>117.6847192535354</v>
       </c>
       <c r="X129" t="n">
-        <v>98.07059937794618</v>
+        <v>98.07059937794617</v>
       </c>
       <c r="Z129" t="n">
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>98.07059937794618</v>
+        <v>98.07059937794617</v>
       </c>
       <c r="AB129" t="n">
         <v>0</v>
@@ -63010,13 +63010,13 @@
         <v>1849.718270643092</v>
       </c>
       <c r="X130" t="n">
-        <v>1541.431892202577</v>
+        <v>1541.431892202576</v>
       </c>
       <c r="Z130" t="n">
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1541.431892202577</v>
+        <v>1541.431892202576</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -63581,7 +63581,7 @@
         <v>3.188439649340365</v>
       </c>
       <c r="BD131" t="n">
-        <v>49187.60162448601</v>
+        <v>49187.601624486</v>
       </c>
       <c r="BE131" t="n">
         <v>40989.66802040501</v>
@@ -63668,16 +63668,16 @@
         <v>3.273092722030352</v>
       </c>
       <c r="CK131" t="n">
-        <v>51703.69735214172</v>
+        <v>51703.6973521417</v>
       </c>
       <c r="CL131" t="n">
-        <v>43086.4144601181</v>
+        <v>43086.41446011809</v>
       </c>
       <c r="CN131" t="n">
         <v>0</v>
       </c>
       <c r="CO131" t="n">
-        <v>43086.4144601181</v>
+        <v>43086.41446011809</v>
       </c>
       <c r="CP131" t="n">
         <v>0</v>
@@ -63755,16 +63755,16 @@
         <v>3.338259998125977</v>
       </c>
       <c r="DR131" t="n">
-        <v>53983.25499233936</v>
+        <v>53983.25499233935</v>
       </c>
       <c r="DS131" t="n">
-        <v>44986.04582694947</v>
+        <v>44986.04582694946</v>
       </c>
       <c r="DU131" t="n">
         <v>0</v>
       </c>
       <c r="DV131" t="n">
-        <v>44986.04582694947</v>
+        <v>44986.04582694946</v>
       </c>
       <c r="DW131" t="n">
         <v>0</v>
@@ -63842,16 +63842,16 @@
         <v>3.404724754688666</v>
       </c>
       <c r="EY131" t="n">
-        <v>56400.73619671605</v>
+        <v>56400.73619671603</v>
       </c>
       <c r="EZ131" t="n">
-        <v>47000.61349726338</v>
+        <v>47000.61349726337</v>
       </c>
       <c r="FB131" t="n">
         <v>0</v>
       </c>
       <c r="FC131" t="n">
-        <v>47000.61349726338</v>
+        <v>47000.61349726337</v>
       </c>
       <c r="FD131" t="n">
         <v>0</v>
@@ -63981,16 +63981,16 @@
         <v>13.06048090830669</v>
       </c>
       <c r="W132" t="n">
-        <v>9331.246026756415</v>
+        <v>9331.246026756413</v>
       </c>
       <c r="X132" t="n">
-        <v>7776.038355630345</v>
+        <v>7776.038355630344</v>
       </c>
       <c r="Z132" t="n">
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>7776.038355630345</v>
+        <v>7776.038355630344</v>
       </c>
       <c r="AB132" t="n">
         <v>0</v>
@@ -64155,16 +64155,16 @@
         <v>10.42757707782553</v>
       </c>
       <c r="CK132" t="n">
-        <v>7782.579910778738</v>
+        <v>7782.579910778739</v>
       </c>
       <c r="CL132" t="n">
-        <v>6485.483258982282</v>
+        <v>6485.483258982283</v>
       </c>
       <c r="CN132" t="n">
         <v>0</v>
       </c>
       <c r="CO132" t="n">
-        <v>6485.483258982282</v>
+        <v>6485.483258982283</v>
       </c>
       <c r="CP132" t="n">
         <v>0</v>
@@ -64468,16 +64468,16 @@
         <v>4.827357362222978</v>
       </c>
       <c r="W133" t="n">
-        <v>5734.399659468786</v>
+        <v>5734.399659468785</v>
       </c>
       <c r="X133" t="n">
-        <v>4778.666382890656</v>
+        <v>4778.666382890655</v>
       </c>
       <c r="Z133" t="n">
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>4778.666382890656</v>
+        <v>4778.666382890655</v>
       </c>
       <c r="AB133" t="n">
         <v>0</v>
@@ -64642,16 +64642,16 @@
         <v>4.510024092660004</v>
       </c>
       <c r="CK133" t="n">
-        <v>5729.047130353633</v>
+        <v>5729.047130353634</v>
       </c>
       <c r="CL133" t="n">
-        <v>4774.205941961361</v>
+        <v>4774.205941961362</v>
       </c>
       <c r="CN133" t="n">
         <v>0</v>
       </c>
       <c r="CO133" t="n">
-        <v>4774.205941961361</v>
+        <v>4774.205941961362</v>
       </c>
       <c r="CP133" t="n">
         <v>0</v>
@@ -64955,16 +64955,16 @@
         <v>3.988971615938908</v>
       </c>
       <c r="W134" t="n">
-        <v>2451.306341933163</v>
+        <v>2451.306341933162</v>
       </c>
       <c r="X134" t="n">
-        <v>2042.755284944303</v>
+        <v>2042.755284944302</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2042.755284944303</v>
+        <v>2042.755284944302</v>
       </c>
       <c r="AB134" t="n">
         <v>0</v>
@@ -65538,7 +65538,7 @@
         <v>0</v>
       </c>
       <c r="BH135" t="n">
-        <v>4321.841140215415</v>
+        <v>4321.841140215414</v>
       </c>
       <c r="BI135" t="n">
         <v>0</v>
@@ -65625,7 +65625,7 @@
         <v>0</v>
       </c>
       <c r="CO135" t="n">
-        <v>4507.043113876402</v>
+        <v>4507.043113876401</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -65712,7 +65712,7 @@
         <v>0</v>
       </c>
       <c r="DV135" t="n">
-        <v>4695.858301072209</v>
+        <v>4695.858301072208</v>
       </c>
       <c r="DW135" t="n">
         <v>0</v>
@@ -65799,7 +65799,7 @@
         <v>0</v>
       </c>
       <c r="FC135" t="n">
-        <v>4889.348685584842</v>
+        <v>4889.348685584841</v>
       </c>
       <c r="FD135" t="n">
         <v>0</v>
@@ -65929,7 +65929,7 @@
         <v>0.1556351833619307</v>
       </c>
       <c r="W136" t="n">
-        <v>157.6403170429446</v>
+        <v>157.6403170429445</v>
       </c>
       <c r="X136" t="n">
         <v>131.3669308691205</v>
@@ -66103,7 +66103,7 @@
         <v>0.03499245820506206</v>
       </c>
       <c r="CK136" t="n">
-        <v>39.39801006525639</v>
+        <v>39.3980100652564</v>
       </c>
       <c r="CL136" t="n">
         <v>32.83167505438033</v>
@@ -66590,16 +66590,16 @@
         <v>0.06998491641012412</v>
       </c>
       <c r="CK137" t="n">
-        <v>85.64825629857465</v>
+        <v>85.64825629857467</v>
       </c>
       <c r="CL137" t="n">
-        <v>71.37354691547887</v>
+        <v>71.37354691547888</v>
       </c>
       <c r="CN137" t="n">
         <v>0</v>
       </c>
       <c r="CO137" t="n">
-        <v>71.37354691547887</v>
+        <v>71.37354691547888</v>
       </c>
       <c r="CP137" t="n">
         <v>0</v>
@@ -66903,7 +66903,7 @@
         <v>0.4054856000904812</v>
       </c>
       <c r="W138" t="n">
-        <v>544.0573268091848</v>
+        <v>544.0573268091847</v>
       </c>
       <c r="X138" t="n">
         <v>453.3811056743207</v>
@@ -67080,13 +67080,13 @@
         <v>459.3448417445339</v>
       </c>
       <c r="CL138" t="n">
-        <v>382.7873681204449</v>
+        <v>382.787368120445</v>
       </c>
       <c r="CN138" t="n">
         <v>0</v>
       </c>
       <c r="CO138" t="n">
-        <v>382.7873681204449</v>
+        <v>382.787368120445</v>
       </c>
       <c r="CP138" t="n">
         <v>0</v>
@@ -67393,13 +67393,13 @@
         <v>4185.082180462128</v>
       </c>
       <c r="X139" t="n">
-        <v>882.5854841229242</v>
+        <v>882.5854841229241</v>
       </c>
       <c r="Z139" t="n">
         <v>182.5151429696739</v>
       </c>
       <c r="AA139" t="n">
-        <v>882.5854841229242</v>
+        <v>882.5854841229241</v>
       </c>
       <c r="AB139" t="n">
         <v>0.2067959945557564</v>
@@ -67973,7 +67973,7 @@
         <v>0</v>
       </c>
       <c r="BH140" t="n">
-        <v>24274.43291348693</v>
+        <v>24274.43291348692</v>
       </c>
       <c r="BI140" t="n">
         <v>0</v>
@@ -68364,7 +68364,7 @@
         <v>0.9597222073752883</v>
       </c>
       <c r="W141" t="n">
-        <v>6540.01352253652</v>
+        <v>6540.013522536519</v>
       </c>
       <c r="X141" t="n">
         <v>5450.011268780433</v>
@@ -68538,16 +68538,16 @@
         <v>0.9165632466239885</v>
       </c>
       <c r="CK141" t="n">
-        <v>6200.325804908129</v>
+        <v>6200.32580490813</v>
       </c>
       <c r="CL141" t="n">
-        <v>5166.938170756774</v>
+        <v>5166.938170756775</v>
       </c>
       <c r="CN141" t="n">
         <v>0</v>
       </c>
       <c r="CO141" t="n">
-        <v>5166.938170756774</v>
+        <v>5166.938170756775</v>
       </c>
       <c r="CP141" t="n">
         <v>0</v>
@@ -69338,7 +69338,7 @@
         <v>6.180782156808317</v>
       </c>
       <c r="W143" t="n">
-        <v>5573.946183065912</v>
+        <v>5573.946183065911</v>
       </c>
       <c r="X143" t="n">
         <v>4777.30392084217</v>
@@ -69837,7 +69837,7 @@
         <v>3736.694297077964</v>
       </c>
       <c r="AB144" t="n">
-        <v>0.6692112668324655</v>
+        <v>0.6692112668324653</v>
       </c>
       <c r="AD144" t="n">
         <v>2316.750464188338</v>
@@ -69876,7 +69876,7 @@
         <v>105.1643424165042</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.6410675831228452</v>
+        <v>0.6410675831228451</v>
       </c>
       <c r="AR144" t="n">
         <v>0</v>
@@ -69987,34 +69987,34 @@
         <v>4929.099929317415</v>
       </c>
       <c r="CG144" t="n">
-        <v>4204.78711277708</v>
+        <v>4204.787112777079</v>
       </c>
       <c r="CH144" t="n">
-        <v>0.1419013984761483</v>
+        <v>0.1419013984761484</v>
       </c>
       <c r="CI144" t="n">
         <v>0</v>
       </c>
       <c r="CJ144" t="n">
-        <v>6.607968390348698</v>
+        <v>6.607968390348697</v>
       </c>
       <c r="CK144" t="n">
-        <v>4561.817376498311</v>
+        <v>4561.81737649831</v>
       </c>
       <c r="CL144" t="n">
-        <v>3891.4753587069</v>
+        <v>3891.475358706899</v>
       </c>
       <c r="CN144" t="n">
-        <v>2788.18360748417</v>
+        <v>2788.183607484169</v>
       </c>
       <c r="CO144" t="n">
-        <v>3891.4753587069</v>
+        <v>3891.475358706899</v>
       </c>
       <c r="CP144" t="n">
         <v>0.7164849704741949</v>
       </c>
       <c r="CR144" t="n">
-        <v>2412.714722398278</v>
+        <v>2412.714722398277</v>
       </c>
       <c r="CS144" t="n">
         <v>0</v>
@@ -70023,10 +70023,10 @@
         <v>0</v>
       </c>
       <c r="CU144" t="n">
-        <v>149.593548343579</v>
+        <v>149.5935483435789</v>
       </c>
       <c r="CV144" t="n">
-        <v>0.62</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="CW144" t="n">
         <v>0</v>
@@ -70038,7 +70038,7 @@
         <v>0.03844134539073311</v>
       </c>
       <c r="DA144" t="n">
-        <v>2654.88885244679</v>
+        <v>2654.888852446789</v>
       </c>
       <c r="DB144" t="n">
         <v>0</v>
@@ -70071,7 +70071,7 @@
         <v>0.002092040502472715</v>
       </c>
       <c r="DM144" t="n">
-        <v>5092.182243041021</v>
+        <v>5092.18224304102</v>
       </c>
       <c r="DN144" t="n">
         <v>4343.905089872309</v>
@@ -70086,7 +70086,7 @@
         <v>6.549807528141967</v>
       </c>
       <c r="DR144" t="n">
-        <v>4625.796776121139</v>
+        <v>4625.796776121138</v>
       </c>
       <c r="DS144" t="n">
         <v>3946.053224620552</v>
@@ -70098,7 +70098,7 @@
         <v>3946.053224620552</v>
       </c>
       <c r="DW144" t="n">
-        <v>0.7374820179403385</v>
+        <v>0.7374820179403384</v>
       </c>
       <c r="DY144" t="n">
         <v>2446.552999264742</v>
@@ -70125,7 +70125,7 @@
         <v>0.042462628004094</v>
       </c>
       <c r="EH144" t="n">
-        <v>2765.582690754313</v>
+        <v>2765.582690754312</v>
       </c>
       <c r="EI144" t="n">
         <v>0</v>
@@ -70134,10 +70134,10 @@
         <v>0</v>
       </c>
       <c r="EK144" t="n">
-        <v>144.5606042388313</v>
+        <v>144.5606042388314</v>
       </c>
       <c r="EL144" t="n">
-        <v>0.7008477922951099</v>
+        <v>0.7008477922951097</v>
       </c>
       <c r="EM144" t="n">
         <v>0</v>
@@ -70179,16 +70179,16 @@
         <v>3957.529089123829</v>
       </c>
       <c r="FB144" t="n">
-        <v>2997.674876896186</v>
+        <v>2997.674876896187</v>
       </c>
       <c r="FC144" t="n">
         <v>3957.529089123829</v>
       </c>
       <c r="FD144" t="n">
-        <v>0.7574612363897626</v>
+        <v>0.7574612363897627</v>
       </c>
       <c r="FF144" t="n">
-        <v>2453.668035256773</v>
+        <v>2453.668035256774</v>
       </c>
       <c r="FG144" t="n">
         <v>0</v>
@@ -70200,7 +70200,7 @@
         <v>183.7740636405065</v>
       </c>
       <c r="FJ144" t="n">
-        <v>0.6199999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="FK144" t="n">
         <v>0</v>
@@ -70224,7 +70224,7 @@
         <v>154.2340422818102</v>
       </c>
       <c r="FS144" t="n">
-        <v>0.7184889284651842</v>
+        <v>0.7184889284651843</v>
       </c>
       <c r="FT144" t="n">
         <v>0</v>
@@ -70312,16 +70312,16 @@
         <v>14.39583311062932</v>
       </c>
       <c r="W145" t="n">
-        <v>671.3463571084008</v>
+        <v>671.3463571084006</v>
       </c>
       <c r="X145" t="n">
-        <v>559.455297590334</v>
+        <v>559.4552975903339</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>559.455297590334</v>
+        <v>559.4552975903339</v>
       </c>
       <c r="AB145" t="n">
         <v>0</v>
@@ -70486,7 +70486,7 @@
         <v>13.74844869935983</v>
       </c>
       <c r="CK145" t="n">
-        <v>652.5087181870093</v>
+        <v>652.5087181870094</v>
       </c>
       <c r="CL145" t="n">
         <v>543.7572651558412</v>
@@ -71286,7 +71286,7 @@
         <v>5.583039327147867</v>
       </c>
       <c r="W147" t="n">
-        <v>4517.250243648209</v>
+        <v>4517.250243648208</v>
       </c>
       <c r="X147" t="n">
         <v>3823.896821547543</v>
@@ -71364,7 +71364,7 @@
         <v>4410.831164698853</v>
       </c>
       <c r="BA147" t="n">
-        <v>0.5115356597065426</v>
+        <v>0.5115356597065427</v>
       </c>
       <c r="BB147" t="n">
         <v>0</v>
@@ -71451,7 +71451,7 @@
         <v>4518.214084793658</v>
       </c>
       <c r="CH147" t="n">
-        <v>0.5140175419917116</v>
+        <v>0.5140175419917119</v>
       </c>
       <c r="CI147" t="n">
         <v>0</v>
@@ -71472,7 +71472,7 @@
         <v>3912.823848208585</v>
       </c>
       <c r="CP147" t="n">
-        <v>0.7400015993170287</v>
+        <v>0.7400015993170286</v>
       </c>
       <c r="CR147" t="n">
         <v>2631.374037920274</v>
@@ -71511,7 +71511,7 @@
         <v>0</v>
       </c>
       <c r="DE147" t="n">
-        <v>0.7400015993170287</v>
+        <v>0.7400015993170286</v>
       </c>
       <c r="DF147" t="n">
         <v>0</v>
@@ -71538,7 +71538,7 @@
         <v>4594.447331603411</v>
       </c>
       <c r="DO147" t="n">
-        <v>0.5126440319793001</v>
+        <v>0.5126440319793002</v>
       </c>
       <c r="DP147" t="n">
         <v>0</v>
@@ -71559,7 +71559,7 @@
         <v>3905.576783686817</v>
       </c>
       <c r="DW147" t="n">
-        <v>0.7601937747071956</v>
+        <v>0.7601937747071955</v>
       </c>
       <c r="DY147" t="n">
         <v>2626.500387029384</v>
@@ -71598,7 +71598,7 @@
         <v>0</v>
       </c>
       <c r="EL147" t="n">
-        <v>0.7601937747071956</v>
+        <v>0.7601937747071955</v>
       </c>
       <c r="EM147" t="n">
         <v>0</v>
@@ -71773,19 +71773,19 @@
         <v>3.044281122121209</v>
       </c>
       <c r="W148" t="n">
-        <v>4332.057213992924</v>
+        <v>4332.057213992923</v>
       </c>
       <c r="X148" t="n">
-        <v>3671.315033184718</v>
+        <v>3671.315033184717</v>
       </c>
       <c r="Z148" t="n">
         <v>2552.854531655214</v>
       </c>
       <c r="AA148" t="n">
-        <v>3671.315033184718</v>
+        <v>3671.315033184717</v>
       </c>
       <c r="AB148" t="n">
-        <v>0.6953515316937308</v>
+        <v>0.6953515316937309</v>
       </c>
       <c r="AD148" t="n">
         <v>2468.959359816722</v>
@@ -71824,7 +71824,7 @@
         <v>0</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.6953515316937308</v>
+        <v>0.6953515316937309</v>
       </c>
       <c r="AR148" t="n">
         <v>0</v>
@@ -71947,19 +71947,19 @@
         <v>3.061958451794335</v>
       </c>
       <c r="CK148" t="n">
-        <v>4485.942575193198</v>
+        <v>4485.942575193199</v>
       </c>
       <c r="CL148" t="n">
-        <v>3801.729201801131</v>
+        <v>3801.729201801132</v>
       </c>
       <c r="CN148" t="n">
         <v>2813.285689503087</v>
       </c>
       <c r="CO148" t="n">
-        <v>3801.729201801131</v>
+        <v>3801.729201801132</v>
       </c>
       <c r="CP148" t="n">
-        <v>0.7400015993170285</v>
+        <v>0.7400015993170282</v>
       </c>
       <c r="CR148" t="n">
         <v>2556.66288821126</v>
@@ -71998,7 +71998,7 @@
         <v>0</v>
       </c>
       <c r="DE148" t="n">
-        <v>0.7400015993170285</v>
+        <v>0.7400015993170282</v>
       </c>
       <c r="DF148" t="n">
         <v>0</v>
@@ -72046,7 +72046,7 @@
         <v>3821.924607589198</v>
       </c>
       <c r="DW148" t="n">
-        <v>0.7601937747071957</v>
+        <v>0.7601937747071956</v>
       </c>
       <c r="DY148" t="n">
         <v>2570.244298603736</v>
@@ -72085,7 +72085,7 @@
         <v>0</v>
       </c>
       <c r="EL148" t="n">
-        <v>0.7601937747071957</v>
+        <v>0.7601937747071956</v>
       </c>
       <c r="EM148" t="n">
         <v>0</v>
@@ -72260,7 +72260,7 @@
         <v>1.088611681244561</v>
       </c>
       <c r="W149" t="n">
-        <v>394.1715764435585</v>
+        <v>394.1715764435584</v>
       </c>
       <c r="X149" t="n">
         <v>328.4763137029654</v>
@@ -72434,7 +72434,7 @@
         <v>1.166415273502069</v>
       </c>
       <c r="CK149" t="n">
-        <v>437.4277218285995</v>
+        <v>437.4277218285996</v>
       </c>
       <c r="CL149" t="n">
         <v>364.523101523833</v>
@@ -72747,16 +72747,16 @@
         <v>4.354446724978244</v>
       </c>
       <c r="W150" t="n">
-        <v>4223.390461390534</v>
+        <v>4223.390461390533</v>
       </c>
       <c r="X150" t="n">
-        <v>3519.492051158779</v>
+        <v>3519.492051158778</v>
       </c>
       <c r="Z150" t="n">
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>3519.492051158779</v>
+        <v>3519.492051158778</v>
       </c>
       <c r="AB150" t="n">
         <v>0</v>
@@ -72921,16 +72921,16 @@
         <v>4.665661094008275</v>
       </c>
       <c r="CK150" t="n">
-        <v>4686.821883315838</v>
+        <v>4686.821883315839</v>
       </c>
       <c r="CL150" t="n">
-        <v>3905.684902763198</v>
+        <v>3905.684902763199</v>
       </c>
       <c r="CN150" t="n">
         <v>0</v>
       </c>
       <c r="CO150" t="n">
-        <v>3905.684902763198</v>
+        <v>3905.684902763199</v>
       </c>
       <c r="CP150" t="n">
         <v>0</v>
@@ -73249,7 +73249,7 @@
         <v>0.289514392378059</v>
       </c>
       <c r="AD151" t="n">
-        <v>316.3123641778062</v>
+        <v>316.3123641778061</v>
       </c>
       <c r="AE151" t="n">
         <v>0</v>
@@ -73312,7 +73312,7 @@
         <v>1238.23899902087</v>
       </c>
       <c r="BA151" t="n">
-        <v>0.0005718135433609831</v>
+        <v>0.0005718135433609832</v>
       </c>
       <c r="BB151" t="n">
         <v>0</v>
@@ -73399,7 +73399,7 @@
         <v>1323.563686640796</v>
       </c>
       <c r="CH151" t="n">
-        <v>0.0006007765204222966</v>
+        <v>0.000600776520422297</v>
       </c>
       <c r="CI151" t="n">
         <v>0</v>
@@ -73420,10 +73420,10 @@
         <v>1250.625500867666</v>
       </c>
       <c r="CP151" t="n">
-        <v>0.3081047551059747</v>
+        <v>0.3081047551059746</v>
       </c>
       <c r="CR151" t="n">
-        <v>350.1751402429465</v>
+        <v>350.1751402429466</v>
       </c>
       <c r="CS151" t="n">
         <v>0</v>
@@ -73459,7 +73459,7 @@
         <v>0</v>
       </c>
       <c r="DE151" t="n">
-        <v>0.3081047551059747</v>
+        <v>0.3081047551059746</v>
       </c>
       <c r="DF151" t="n">
         <v>0</v>
@@ -73486,7 +73486,7 @@
         <v>1421.493885276429</v>
       </c>
       <c r="DO151" t="n">
-        <v>0.0006288057436327886</v>
+        <v>0.0006288057436327888</v>
       </c>
       <c r="DP151" t="n">
         <v>0</v>
@@ -73501,13 +73501,13 @@
         <v>1318.36287433655</v>
       </c>
       <c r="DU151" t="n">
-        <v>417.2775464166609</v>
+        <v>417.2775464166608</v>
       </c>
       <c r="DV151" t="n">
         <v>1318.36287433655</v>
       </c>
       <c r="DW151" t="n">
-        <v>0.3165119061977915</v>
+        <v>0.3165119061977914</v>
       </c>
       <c r="DY151" t="n">
         <v>369.141604814234</v>
@@ -73534,7 +73534,7 @@
         <v>0</v>
       </c>
       <c r="EH151" t="n">
-        <v>417.2775464166609</v>
+        <v>417.2775464166608</v>
       </c>
       <c r="EI151" t="n">
         <v>0</v>
@@ -73546,7 +73546,7 @@
         <v>0</v>
       </c>
       <c r="EL151" t="n">
-        <v>0.3165119061977915</v>
+        <v>0.3165119061977914</v>
       </c>
       <c r="EM151" t="n">
         <v>0</v>
@@ -73721,7 +73721,7 @@
         <v>3.032079658161078</v>
       </c>
       <c r="W152" t="n">
-        <v>1866.629333065164</v>
+        <v>1866.629333065163</v>
       </c>
       <c r="X152" t="n">
         <v>1555.52444422097</v>
@@ -74382,7 +74382,7 @@
         <v>3.962710608572594</v>
       </c>
       <c r="CK153" t="n">
-        <v>24435.19235188526</v>
+        <v>24435.19235188527</v>
       </c>
       <c r="CL153" t="n">
         <v>20362.66029323772</v>
@@ -74695,16 +74695,16 @@
         <v>2.021386438774052</v>
       </c>
       <c r="W154" t="n">
-        <v>12834.26497173336</v>
+        <v>12834.26497173335</v>
       </c>
       <c r="X154" t="n">
-        <v>10695.2208097778</v>
+        <v>10695.22080977779</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>10695.2208097778</v>
+        <v>10695.22080977779</v>
       </c>
       <c r="AB154" t="n">
         <v>0</v>
@@ -75185,13 +75185,13 @@
         <v>5820.247413666852</v>
       </c>
       <c r="X155" t="n">
-        <v>4850.206178055711</v>
+        <v>4850.20617805571</v>
       </c>
       <c r="Z155" t="n">
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>4850.206178055711</v>
+        <v>4850.20617805571</v>
       </c>
       <c r="AB155" t="n">
         <v>0</v>
@@ -75356,16 +75356,16 @@
         <v>2.765838544659228</v>
       </c>
       <c r="CK155" t="n">
-        <v>6779.889406160839</v>
+        <v>6779.88940616084</v>
       </c>
       <c r="CL155" t="n">
-        <v>5649.907838467366</v>
+        <v>5649.907838467367</v>
       </c>
       <c r="CN155" t="n">
         <v>0</v>
       </c>
       <c r="CO155" t="n">
-        <v>5649.907838467366</v>
+        <v>5649.907838467367</v>
       </c>
       <c r="CP155" t="n">
         <v>0</v>
@@ -75669,7 +75669,7 @@
         <v>3.943465567603182</v>
       </c>
       <c r="W156" t="n">
-        <v>4526.982927421111</v>
+        <v>4526.98292742111</v>
       </c>
       <c r="X156" t="n">
         <v>3772.485772850926</v>
@@ -76156,7 +76156,7 @@
         <v>0.797913446682298</v>
       </c>
       <c r="W157" t="n">
-        <v>768.2990976727824</v>
+        <v>768.2990976727823</v>
       </c>
       <c r="X157" t="n">
         <v>640.2492480606521</v>
@@ -76330,16 +76330,16 @@
         <v>0.7800275179581209</v>
       </c>
       <c r="CK157" t="n">
-        <v>764.3763668958786</v>
+        <v>764.3763668958787</v>
       </c>
       <c r="CL157" t="n">
-        <v>636.9803057465657</v>
+        <v>636.9803057465658</v>
       </c>
       <c r="CN157" t="n">
         <v>0</v>
       </c>
       <c r="CO157" t="n">
-        <v>636.9803057465657</v>
+        <v>636.9803057465658</v>
       </c>
       <c r="CP157" t="n">
         <v>0</v>
